--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 51149-2025</t>
+          <t>A 27330-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45947</v>
+        <v>45812</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1086,21 +1086,142 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
       </c>
       <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp
+Bredbrämad bastardsvärmare
+Frygisk spindling
+Grangråticka
+Kopparspindling
+Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Tvillingspindling
+Rosenticka
+Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 51149-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
         <v>19</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>19</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Läderdoftande fingersvamp
 Svart taggsvamp
@@ -1116,153 +1237,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 27330-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45812</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>13</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp
-Bredbrämad bastardsvärmare
-Frygisk spindling
-Grangråticka
-Kopparspindling
-Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Tvillingspindling
-Rosenticka
-Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45771</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45684</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45810</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46247</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58480-2025</t>
+          <t>A 62278-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45985</v>
+        <v>46006</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2581,17 +2581,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2614,12 +2614,129 @@
         <v>4</v>
       </c>
       <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Rökfingersvamp
+Vanlig sandviol
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 58480-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
         <v>9</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart trolldruva
@@ -2627,160 +2744,43 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 62278-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Rökfingersvamp
-Vanlig sandviol
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21700-2024</t>
+          <t>A 61685-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45442</v>
+        <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,14 +2811,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -2827,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2851,384 +2851,384 @@
         <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33463-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Bredgentiana
+Fältgentiana
+Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 33463-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Bredgentiana
-Fältgentiana
-Slåtterfibbla</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45985</v>
+        <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3259,23 +3259,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3287,56 +3287,52 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
@@ -3360,7 +3356,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3467,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3561,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3579,10 +3575,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3596,23 +3592,23 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3624,52 +3620,56 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45428</v>
+        <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,20 +3816,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3844,55 +3849,55 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3906,10 +3911,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45428</v>
+        <v>46009</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3921,17 +3926,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3946,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3955,53 +3965,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4015,10 +4021,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45947</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4036,13 +4042,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4076,42 +4082,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4125,10 +4131,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46099</v>
+        <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4140,20 +4146,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4165,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4181,42 +4192,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4226,14 +4237,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44970</v>
+        <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4251,13 +4262,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4291,42 +4302,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4340,10 +4351,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45981</v>
+        <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4385,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4401,42 +4412,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4450,10 +4461,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4465,13 +4476,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4480,10 +4486,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4498,55 +4504,55 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4556,14 +4562,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45993</v>
+        <v>44533</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4575,19 +4581,14 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>18.6</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4614,49 +4615,53 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4666,14 +4671,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45999</v>
+        <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4691,7 +4696,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4700,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4718,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4731,46 +4736,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4780,14 +4781,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46009</v>
+        <v>45993</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4806,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>18.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4838,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4849,38 +4850,38 @@
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4890,14 +4891,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44533</v>
+        <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,8 +4910,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4919,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4934,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4946,50 +4952,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4999,14 +5005,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46034</v>
+        <v>44970</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5030,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5064,42 +5070,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5113,10 +5119,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46044</v>
+        <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,7 +5140,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5178,38 +5184,38 @@
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5223,10 +5229,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5238,20 +5244,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5263,10 +5274,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5279,42 +5290,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5328,10 +5339,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45183</v>
+        <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5343,13 +5354,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5361,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5373,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5385,39 +5391,39 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
@@ -5441,7 +5447,7 @@
         <v>45684</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5529,7 +5535,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5543,10 +5549,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5558,22 +5564,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5588,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5600,46 +5601,50 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5653,10 +5658,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5668,25 +5673,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5698,10 +5698,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5714,35 +5714,35 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
         <v>44803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44803</v>
+        <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45309</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6007,13 +6007,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6056,7 +6051,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6070,10 +6065,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>46009</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6085,8 +6080,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6129,7 +6129,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45576</v>
+        <v>45800</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44676</v>
+        <v>46010</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45835</v>
+        <v>46003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46071</v>
+        <v>46044</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6394,11 +6394,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6441,7 +6441,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45918</v>
+        <v>45835</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45925</v>
+        <v>45918</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6548,8 +6548,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6592,7 +6597,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6606,10 +6611,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46083</v>
+        <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6621,13 +6626,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46085</v>
+        <v>46071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45944</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45947</v>
+        <v>46083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46099</v>
+        <v>45947</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7011,8 +7011,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7055,7 +7060,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44740</v>
+        <v>46085</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7084,8 +7089,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7128,7 +7138,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7142,10 +7152,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45954</v>
+        <v>45715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7157,13 +7167,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7206,7 +7211,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7220,10 +7225,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45954</v>
+        <v>45309</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7235,13 +7240,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7284,7 +7284,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45958</v>
+        <v>46099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7313,13 +7313,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7362,7 +7357,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7376,10 +7371,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7397,7 +7392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7440,7 +7435,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7450,14 +7445,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45978</v>
+        <v>45954</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7475,7 +7470,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7518,7 +7513,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7532,10 +7527,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45982</v>
+        <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7553,7 +7548,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7596,7 +7591,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7610,10 +7605,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46122</v>
+        <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7627,11 +7622,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7674,7 +7669,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7688,10 +7683,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45994</v>
+        <v>46122</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7703,8 +7698,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7747,7 +7747,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45999</v>
+        <v>45978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7825,7 +7825,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45982</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7856,11 +7856,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7932,13 +7932,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7981,7 +7976,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7991,14 +7986,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46009</v>
+        <v>45999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8016,7 +8011,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8059,7 +8054,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8073,10 +8068,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8090,7 +8085,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -8137,7 +8132,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8151,10 +8146,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8168,11 +8163,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8215,7 +8210,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8229,10 +8224,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46044</v>
+        <v>45819</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8246,11 +8241,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8293,7 +8288,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8307,10 +8302,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45174</v>
+        <v>45013</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8322,13 +8317,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8371,7 +8361,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8381,14 +8371,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45819</v>
+        <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8406,7 +8396,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8449,7 +8439,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8463,10 +8453,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45309</v>
+        <v>46247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8478,8 +8468,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8522,7 +8517,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8536,10 +8531,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45196</v>
+        <v>46206</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8553,11 +8548,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8600,7 +8595,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8614,10 +8609,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45174</v>
+        <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8631,11 +8626,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8678,7 +8673,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8692,10 +8687,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45561</v>
+        <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8709,11 +8704,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8756,7 +8751,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8791,7 +8786,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8834,7 +8829,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8848,10 +8843,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46206</v>
+        <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8865,7 +8860,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -8912,7 +8907,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8926,10 +8921,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>45161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8943,11 +8938,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8990,7 +8985,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9004,10 +8999,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46255</v>
+        <v>45576</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9021,11 +9016,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9068,7 +9063,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9082,10 +9077,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>45561</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9099,11 +9094,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9146,7 +9141,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9160,10 +9155,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45013</v>
+        <v>44740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9176,7 +9171,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9219,7 +9214,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9233,10 +9228,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45715</v>
+        <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9248,8 +9243,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45800</v>
+        <v>45174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 27330-2025</t>
+          <t>A 51149-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45812</v>
+        <v>45947</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1086,21 +1086,142 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
       </c>
       <c r="T5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U5" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp
+Svart taggsvamp
+Ullticka
+Vårärt
+Guldlockmossa
+Mindre märgborre
+Mörk husmossa
+Platt fjädermossa
+Skogsknipprot
+Stubbspretmossa
+Tibast
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 27330-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
         <v>13</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>8</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Bitter taggsvamp
 Bredbrämad bastardsvärmare
@@ -1116,153 +1237,32 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 51149-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>19</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Läderdoftande fingersvamp
-Svart taggsvamp
-Ullticka
-Vårärt
-Guldlockmossa
-Mindre märgborre
-Mörk husmossa
-Platt fjädermossa
-Skogsknipprot
-Stubbspretmossa
-Tibast
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45771</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 3949-2025</t>
+          <t>A 46508-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45684</v>
+        <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1557,21 +1557,142 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
         <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grangråticka
+Knärot
+Kopparspindling
+Tretåig hackspett
+Vedtrappmossa
+Nästrot
+Svart trolldruva
+Trådfräken
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 46508-2025 artfynd.xlsx", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 46508-2025 karta.png", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 46508-2025 georefererad karta.tif", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 46508-2025 karta knärot.png", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 46508-2025 FSC-klagomål.docx", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 46508-2025 FSC-klagomål mail.docx", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 46508-2025 tillsynsbegäran.docx", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 46508-2025 tillsynsbegäran mail.docx", "A 46508-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 46508-2025 prioriterade fågelarter.docx", "A 46508-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 3949-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
         <v>67</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sanddraba
 Toppjungfrulin
@@ -1584,153 +1705,32 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3949-2025 artfynd.xlsx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3949-2025 karta.png", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3949-2025 georefererad karta.tif", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3949-2025 FSC-klagomål.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3949-2025 FSC-klagomål mail.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3949-2025 tillsynsbegäran.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3949-2025 tillsynsbegäran mail.docx", "A 3949-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46508-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45925</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>17</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grangråticka
-Knärot
-Kopparspindling
-Tretåig hackspett
-Vedtrappmossa
-Nästrot
-Svart trolldruva
-Trådfräken
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 46508-2025 artfynd.xlsx", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 46508-2025 karta.png", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 46508-2025 georefererad karta.tif", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 46508-2025 karta knärot.png", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 46508-2025 FSC-klagomål.docx", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 46508-2025 FSC-klagomål mail.docx", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 46508-2025 tillsynsbegäran.docx", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 46508-2025 tillsynsbegäran mail.docx", "A 46508-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 46508-2025 prioriterade fågelarter.docx", "A 46508-2025")</f>
         <v/>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
         <v>45526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45810</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46247</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 62278-2025</t>
+          <t>A 58480-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46006</v>
+        <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2614,12 +2614,129 @@
         <v>4</v>
       </c>
       <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Svart trolldruva
+Tibast
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 62278-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
         <v>6</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Rökfingersvamp
@@ -2627,160 +2744,43 @@
 Vårstarr</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 58480-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Svart trolldruva
-Tibast
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61685-2025</t>
+          <t>A 61693-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2797,7 +2797,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,17 +2815,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2848,387 +2848,387 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Klasefibbla
 Tvåblad
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 33463-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D23" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="I23" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33463-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>7</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bredgentiana
 Fältgentiana
 Slåtterfibbla</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 21700-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3259,23 +3259,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3287,52 +3287,56 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -3356,7 +3360,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3471,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3565,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3575,10 +3579,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3592,23 +3596,23 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3620,56 +3624,52 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44623</v>
+        <v>45428</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,25 +3816,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3849,55 +3844,55 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3911,10 +3906,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46009</v>
+        <v>46099</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,25 +3921,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3956,58 +3946,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4021,10 +4011,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>45428</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4036,22 +4026,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4066,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4078,46 +4063,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4131,10 +4120,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46044</v>
+        <v>45947</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,17 +4137,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4192,42 +4181,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4241,10 +4230,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45947</v>
+        <v>45981</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4262,7 +4251,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4274,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4286,10 +4275,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4302,42 +4291,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4347,14 +4336,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>45993</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,13 +4361,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>18.6</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4405,49 +4394,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4457,14 +4446,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46099</v>
+        <v>44970</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,20 +4465,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4501,10 +4495,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4517,42 +4511,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4562,14 +4556,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44533</v>
+        <v>45999</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4581,8 +4575,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4591,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4606,7 +4605,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4618,50 +4617,50 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4675,10 +4674,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45981</v>
+        <v>46009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4696,19 +4695,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4720,58 +4719,58 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4781,14 +4780,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45993</v>
+        <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4802,20 +4801,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18.6</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4830,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4839,49 +4838,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4891,14 +4890,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45999</v>
+        <v>46034</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4916,16 +4915,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4940,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4956,46 +4955,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5005,14 +5000,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44970</v>
+        <v>46044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5026,14 +5021,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -5070,42 +5065,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5119,10 +5114,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46206</v>
+        <v>44533</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,19 +5129,14 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5176,46 +5166,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5229,10 +5223,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5244,25 +5238,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5274,10 +5263,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5290,42 +5279,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5339,10 +5328,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5354,20 +5343,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5379,10 +5373,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5391,46 +5385,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5440,14 +5434,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45684</v>
+        <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,17 +5453,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5484,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5493,49 +5492,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5549,10 +5548,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45428</v>
+        <v>45183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5564,8 +5563,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5574,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5589,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5601,50 +5605,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5683,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5701,48 +5701,48 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
         <v>44803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45196</v>
+        <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45309</v>
+        <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6007,8 +6007,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6051,7 +6056,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6065,10 +6070,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46009</v>
+        <v>46083</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6086,7 +6091,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6129,7 +6134,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6143,10 +6148,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45800</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6158,13 +6163,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46010</v>
+        <v>46085</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46003</v>
+        <v>46099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6314,13 +6314,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6363,7 +6358,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46044</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6394,11 +6389,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6441,7 +6436,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6455,10 +6450,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45835</v>
+        <v>45918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6476,7 +6471,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6519,7 +6514,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6533,10 +6528,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45918</v>
+        <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6554,7 +6549,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
         <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6670,7 +6665,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6684,10 +6679,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46071</v>
+        <v>46122</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6701,11 +6696,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6748,7 +6743,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6758,14 +6753,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45944</v>
+        <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6783,7 +6778,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6826,7 +6821,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6836,14 +6831,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
         <v>45944</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6861,7 +6856,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6904,7 +6899,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6918,10 +6913,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46083</v>
+        <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6939,7 +6934,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6999,7 +6994,7 @@
         <v>45947</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7060,7 +7055,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7074,10 +7069,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46085</v>
+        <v>45954</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7095,7 +7090,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7138,7 +7133,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7152,10 +7147,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45715</v>
+        <v>45954</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7167,8 +7162,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45309</v>
+        <v>45958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7240,8 +7240,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7284,7 +7289,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7298,10 +7303,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46099</v>
+        <v>45958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7313,8 +7318,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7357,7 +7367,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7371,10 +7381,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45954</v>
+        <v>45174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7392,7 +7402,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7435,7 +7445,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7445,14 +7455,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45954</v>
+        <v>45978</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7470,7 +7480,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7513,7 +7523,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7527,10 +7537,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45958</v>
+        <v>45982</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7548,7 +7558,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7591,7 +7601,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7605,10 +7615,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45958</v>
+        <v>45819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7626,7 +7636,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7669,7 +7679,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7683,10 +7693,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46122</v>
+        <v>45994</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7698,13 +7708,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7747,7 +7752,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7757,14 +7762,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45978</v>
+        <v>45561</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7782,7 +7787,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7825,7 +7830,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7835,14 +7840,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45982</v>
+        <v>45999</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7860,7 +7865,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7903,7 +7908,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7917,10 +7922,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45994</v>
+        <v>44740</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7933,7 +7938,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7976,7 +7981,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7986,14 +7991,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8007,11 +8012,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8054,7 +8059,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8071,7 +8076,7 @@
         <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8089,7 +8094,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8132,7 +8137,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8146,10 +8151,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8163,11 +8168,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8210,7 +8215,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8224,10 +8229,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45819</v>
+        <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8245,7 +8250,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8288,7 +8293,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8302,10 +8307,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45013</v>
+        <v>46003</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8317,8 +8322,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8361,7 +8371,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8371,14 +8381,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44803</v>
+        <v>46044</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8392,11 +8402,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8439,7 +8449,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8453,10 +8463,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46247</v>
+        <v>46071</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8470,11 +8480,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8517,7 +8527,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8531,10 +8541,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46206</v>
+        <v>45174</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8548,11 +8558,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8595,7 +8605,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8609,10 +8619,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46206</v>
+        <v>45309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8624,13 +8634,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8673,7 +8678,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8687,10 +8692,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46255</v>
+        <v>46247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8708,7 +8713,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8751,7 +8756,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46261</v>
+        <v>46206</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8786,7 +8791,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8829,7 +8834,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8843,10 +8848,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44676</v>
+        <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8860,11 +8865,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8907,7 +8912,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8921,10 +8926,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45161</v>
+        <v>46255</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8938,11 +8943,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8985,7 +8990,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8999,10 +9004,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45576</v>
+        <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9016,11 +9021,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9063,7 +9068,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9077,10 +9082,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45561</v>
+        <v>45013</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9092,13 +9097,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44740</v>
+        <v>45715</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45174</v>
+        <v>45800</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45174</v>
+        <v>45835</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 51149-2025</t>
+          <t>A 27330-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45947</v>
+        <v>45812</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1086,21 +1086,142 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
       </c>
       <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp
+Bredbrämad bastardsvärmare
+Frygisk spindling
+Grangråticka
+Kopparspindling
+Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Tvillingspindling
+Rosenticka
+Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 51149-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
         <v>19</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>19</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Läderdoftande fingersvamp
 Svart taggsvamp
@@ -1116,153 +1237,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 27330-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45812</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>13</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp
-Bredbrämad bastardsvärmare
-Frygisk spindling
-Grangråticka
-Kopparspindling
-Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Tvillingspindling
-Rosenticka
-Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
         <v>45684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45771</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46508-2025</t>
+          <t>A 3949-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45925</v>
+        <v>45684</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,45 +1533,158 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>67</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Sanddraba
+Toppjungfrulin
+Vanlig sandviol
+Skogsknipprot
+Tvåblad
+Fläcknycklar
+Kärrknipprot
+Nattviol
+Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3949-2025 artfynd.xlsx", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3949-2025 karta.png", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3949-2025 georefererad karta.tif", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3949-2025 FSC-klagomål.docx", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3949-2025 FSC-klagomål mail.docx", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3949-2025 tillsynsbegäran.docx", "A 3949-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3949-2025 tillsynsbegäran mail.docx", "A 3949-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46508-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
         <v>17</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grangråticka
 Knärot
@@ -1584,153 +1697,40 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 46508-2025 artfynd.xlsx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 46508-2025 karta.png", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 46508-2025 georefererad karta.tif", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 46508-2025 karta knärot.png", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 46508-2025 FSC-klagomål.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 46508-2025 FSC-klagomål mail.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 46508-2025 tillsynsbegäran.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 46508-2025 tillsynsbegäran mail.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 46508-2025 prioriterade fågelarter.docx", "A 46508-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 3949-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>67</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Sanddraba
-Toppjungfrulin
-Vanlig sandviol
-Skogsknipprot
-Tvåblad
-Fläcknycklar
-Kärrknipprot
-Nattviol
-Ängsnycklar</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3949-2025 artfynd.xlsx", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3949-2025 karta.png", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3949-2025 georefererad karta.tif", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3949-2025 FSC-klagomål.docx", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3949-2025 FSC-klagomål mail.docx", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3949-2025 tillsynsbegäran.docx", "A 3949-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3949-2025 tillsynsbegäran mail.docx", "A 3949-2025")</f>
         <v/>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
         <v>45526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45638</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45810</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46247</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45985</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61693-2025</t>
+          <t>A 61685-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2797,7 +2797,7 @@
         <v>46002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,16 +2815,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2848,268 +2848,268 @@
         <v>3</v>
       </c>
       <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>4</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vedtrappmossa
 Brandticka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 21700-2024</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1.1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
         <v>46247</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45985</v>
+        <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3259,23 +3259,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3287,56 +3287,52 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
@@ -3360,7 +3356,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3467,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3561,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3579,10 +3575,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3596,23 +3592,23 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3624,52 +3620,56 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45428</v>
+        <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,20 +3816,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3844,55 +3849,55 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3906,10 +3911,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46099</v>
+        <v>46034</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3921,20 +3926,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3946,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3962,42 +3972,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4011,10 +4021,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45428</v>
+        <v>45183</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4026,8 +4036,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4036,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4051,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4063,50 +4078,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4120,10 +4131,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45947</v>
+        <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4137,17 +4148,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4181,42 +4192,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4230,10 +4241,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45981</v>
+        <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4251,7 +4262,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4263,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4275,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4291,42 +4302,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4336,14 +4347,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45993</v>
+        <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,19 +4366,14 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>18.6</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4394,49 +4400,53 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4446,14 +4456,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44970</v>
+        <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,19 +4481,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4495,10 +4505,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4511,42 +4521,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4560,10 +4570,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4581,16 +4591,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.5</v>
+        <v>18.6</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4605,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4614,53 +4624,49 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4670,14 +4676,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46009</v>
+        <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4695,16 +4701,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4719,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4728,49 +4734,53 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4784,10 +4794,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44623</v>
+        <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,20 +4811,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4829,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4841,46 +4851,46 @@
         <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4894,10 +4904,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46034</v>
+        <v>46099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,25 +4919,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4939,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4955,42 +4960,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5000,14 +5005,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46044</v>
+        <v>44970</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5021,14 +5026,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -5065,42 +5070,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5114,10 +5119,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44533</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5130,7 +5135,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5142,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5154,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5170,46 +5175,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5219,14 +5220,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45428</v>
+        <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5239,7 +5240,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5248,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5266,55 +5267,55 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5328,10 +5329,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5343,22 +5344,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5373,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5385,46 +5381,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5441,7 +5441,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5503,38 +5503,38 @@
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45183</v>
+        <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,17 +5565,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5609,42 +5609,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45684</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5683,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5701,48 +5701,48 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
         <v>44803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44803</v>
+        <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45196</v>
+        <v>45309</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6007,13 +6007,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6056,7 +6051,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6070,10 +6065,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46083</v>
+        <v>45800</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6091,7 +6086,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6134,7 +6129,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6148,10 +6143,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6163,8 +6158,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46085</v>
+        <v>45918</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46099</v>
+        <v>45925</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>46044</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,11 +6389,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45918</v>
+        <v>45715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6465,13 +6465,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6514,7 +6509,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6524,14 +6519,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45576</v>
+        <v>45944</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6549,7 +6544,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6592,7 +6587,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6606,10 +6601,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45925</v>
+        <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6621,8 +6616,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46122</v>
+        <v>45309</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6694,13 +6694,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6743,7 +6738,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6757,10 +6752,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44676</v>
+        <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6778,7 +6773,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6821,7 +6816,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6831,14 +6826,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6856,7 +6851,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6899,7 +6894,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6913,10 +6908,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6934,7 +6929,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6977,7 +6972,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6991,10 +6986,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45947</v>
+        <v>45958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7012,7 +7007,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7055,7 +7050,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7069,10 +7064,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7090,7 +7085,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7133,7 +7128,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7143,14 +7138,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45954</v>
+        <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7168,7 +7163,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7211,7 +7206,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7225,10 +7220,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45958</v>
+        <v>46071</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7246,7 +7241,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7289,7 +7284,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7303,10 +7298,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45958</v>
+        <v>45982</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7324,7 +7319,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7367,7 +7362,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7381,10 +7376,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45174</v>
+        <v>46083</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7402,7 +7397,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7445,7 +7440,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7455,14 +7450,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7474,13 +7469,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7523,7 +7513,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7533,14 +7523,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45982</v>
+        <v>45999</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7558,7 +7548,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7601,7 +7591,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7615,10 +7605,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45819</v>
+        <v>46085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7679,7 +7669,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7693,10 +7683,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7708,8 +7698,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7752,7 +7747,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7766,10 +7761,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45561</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7783,11 +7778,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7830,7 +7825,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7840,14 +7835,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7865,7 +7860,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7908,7 +7903,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7922,10 +7917,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44740</v>
+        <v>46010</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7937,8 +7932,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,11 +8012,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8059,7 +8059,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>45013</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8088,13 +8088,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8137,7 +8132,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8151,10 +8146,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46009</v>
+        <v>46099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8166,13 +8161,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8215,7 +8205,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8229,10 +8219,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46010</v>
+        <v>46122</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8246,11 +8236,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8293,7 +8283,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8303,14 +8293,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46003</v>
+        <v>44803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8328,7 +8318,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8371,7 +8361,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8385,10 +8375,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46044</v>
+        <v>45819</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8402,11 +8392,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8449,7 +8439,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8463,10 +8453,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46071</v>
+        <v>44676</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8484,7 +8474,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8527,7 +8517,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8541,10 +8531,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45174</v>
+        <v>45161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8562,7 +8552,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8605,7 +8595,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8619,10 +8609,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45309</v>
+        <v>45576</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8634,8 +8624,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8678,7 +8673,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8692,10 +8687,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46247</v>
+        <v>45561</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8709,11 +8704,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8756,7 +8751,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46206</v>
+        <v>44740</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8785,13 +8780,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8834,7 +8824,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8848,10 +8838,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46206</v>
+        <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8869,7 +8859,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8912,7 +8902,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8926,10 +8916,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46255</v>
+        <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8947,7 +8937,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8990,7 +8980,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9004,10 +8994,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46261</v>
+        <v>46206</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9025,7 +9015,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9068,7 +9058,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9082,10 +9072,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45013</v>
+        <v>46255</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9097,8 +9087,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9141,7 +9136,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9155,10 +9150,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45715</v>
+        <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9170,8 +9165,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45800</v>
+        <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9245,11 +9245,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45835</v>
+        <v>45174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,80 +1027,324 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
+          <t>A 33463-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U5" t="n">
+        <v>16</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Bredgentiana
+Fältgentiana
+Odörspindling
+Slåtterfibbla
+Ullticka
+Vårärt
+Anisspindling
+Bronshjon
+Skogsknipprot
+Thomsons trägnagare
+Tibast
+Blåsippa
+Kransmossa
+Ormbär</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 51149-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19</v>
+      </c>
+      <c r="U6" t="n">
+        <v>19</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp
+Svart taggsvamp
+Ullticka
+Vårärt
+Guldlockmossa
+Mindre märgborre
+Mörk husmossa
+Platt fjädermossa
+Skogsknipprot
+Stubbspretmossa
+Tibast
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>A 27330-2025</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45812</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>11</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R7" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S7" t="n">
         <v>12</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>13</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>8</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bitter taggsvamp
 Bredbrämad bastardsvärmare
@@ -1116,228 +1360,107 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 51149-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 3954-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>19</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Läderdoftande fingersvamp
-Svart taggsvamp
-Ullticka
-Vårärt
-Guldlockmossa
-Mindre märgborre
-Mörk husmossa
-Platt fjädermossa
-Skogsknipprot
-Stubbspretmossa
-Tibast
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3954-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45684</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>11</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>25</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Sanddraba
 Backklöver
@@ -1352,112 +1475,112 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3954-2025 artfynd.xlsx", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3954-2025 karta.png", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3954-2025 georefererad karta.tif", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3954-2025 FSC-klagomål.docx", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3954-2025 FSC-klagomål mail.docx", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3954-2025 tillsynsbegäran.docx", "A 3954-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3954-2025 tillsynsbegäran mail.docx", "A 3954-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 19703-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>45771</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>3.8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>7</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>19</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kattfotslav
@@ -1471,107 +1594,107 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19703-2025 artfynd.xlsx", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19703-2025 karta.png", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19703-2025 georefererad karta.tif", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19703-2025 FSC-klagomål.docx", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19703-2025 FSC-klagomål mail.docx", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19703-2025 tillsynsbegäran.docx", "A 19703-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19703-2025 tillsynsbegäran mail.docx", "A 19703-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 3949-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45684</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>5.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>67</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Sanddraba
 Toppjungfrulin
@@ -1584,107 +1707,107 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3949-2025 artfynd.xlsx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3949-2025 karta.png", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3949-2025 georefererad karta.tif", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3949-2025 FSC-klagomål.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3949-2025 FSC-klagomål mail.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3949-2025 tillsynsbegäran.docx", "A 3949-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3949-2025 tillsynsbegäran mail.docx", "A 3949-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 46508-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45925</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>6.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>9</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>17</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grangråticka
 Knärot
@@ -1697,120 +1820,120 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 46508-2025 artfynd.xlsx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 46508-2025 karta.png", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 46508-2025 georefererad karta.tif", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 46508-2025 karta knärot.png", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 46508-2025 FSC-klagomål.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 46508-2025 FSC-klagomål mail.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 46508-2025 tillsynsbegäran.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 46508-2025 tillsynsbegäran mail.docx", "A 46508-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 46508-2025 prioriterade fågelarter.docx", "A 46508-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 34798-2024</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45526</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>13.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>8</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>11</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Gullpudra
@@ -1822,111 +1945,111 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 34798-2024 artfynd.xlsx", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 34798-2024 karta.png", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 34798-2024 georefererad karta.tif", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 34798-2024 FSC-klagomål.docx", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 34798-2024 FSC-klagomål mail.docx", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 34798-2024 tillsynsbegäran.docx", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 34798-2024 tillsynsbegäran mail.docx", "A 34798-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 34798-2024 prioriterade fågelarter.docx", "A 34798-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 3952-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45684</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>7</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>22</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Sexfläckig bastardsvärmare
@@ -1937,112 +2060,112 @@
 Ängsnycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3952-2025 artfynd.xlsx", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3952-2025 karta.png", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3952-2025 georefererad karta.tif", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3952-2025 FSC-klagomål.docx", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3952-2025 FSC-klagomål mail.docx", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3952-2025 tillsynsbegäran.docx", "A 3952-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3952-2025 tillsynsbegäran mail.docx", "A 3952-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>S 5067-2024</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45638</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>118.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>7</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>8</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsklocka
 Turkos blåvinge
@@ -2053,116 +2176,116 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 5067-2024 artfynd.xlsx", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 5067-2024 karta.png", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 5067-2024 georefererad karta.tif", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 5067-2024 FSC-klagomål.docx", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 5067-2024 FSC-klagomål mail.docx", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 5067-2024 tillsynsbegäran.docx", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 5067-2024 tillsynsbegäran mail.docx", "S 5067-2024")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/S 5067-2024 prioriterade fågelarter.docx", "S 5067-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 26681-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45810</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>3.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
         <v>6</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>18</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Nästrot
@@ -2172,112 +2295,112 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 26681-2025 artfynd.xlsx", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 26681-2025 karta.png", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 26681-2025 georefererad karta.tif", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 26681-2025 FSC-klagomål.docx", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 26681-2025 FSC-klagomål mail.docx", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 26681-2025 tillsynsbegäran.docx", "A 26681-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 26681-2025 tillsynsbegäran mail.docx", "A 26681-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 22563-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>3.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>5</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Backruta
 Klasefibbla
@@ -2286,112 +2409,112 @@
 Tibast</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 22563-2026 artfynd.xlsx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 22563-2026 karta.png", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 22563-2026 georefererad karta.tif", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 22563-2026 FSC-klagomål.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 22563-2026 FSC-klagomål mail.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 22563-2026 tillsynsbegäran.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 22563-2026 tillsynsbegäran mail.docx", "A 22563-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 33464-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>5.1</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>5</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skrovlig taggsvamp
 Grantaggsvamp
@@ -2400,112 +2523,112 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33464-2026 artfynd.xlsx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33464-2026 karta.png", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33464-2026 georefererad karta.tif", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33464-2026 FSC-klagomål.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33464-2026 FSC-klagomål mail.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33464-2026 tillsynsbegäran.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33464-2026 tillsynsbegäran mail.docx", "A 33464-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>S 4507-2023</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45274</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>11.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>3</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>11</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Stor bockrot
 Kattunvisslare
@@ -2514,112 +2637,112 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 4507-2023 artfynd.xlsx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 4507-2023 karta.png", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 4507-2023 georefererad karta.tif", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 4507-2023 FSC-klagomål.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 4507-2023 FSC-klagomål mail.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 4507-2023 tillsynsbegäran.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 4507-2023 tillsynsbegäran mail.docx", "S 4507-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 58480-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>4.1</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
         <v>4</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>9</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart trolldruva
@@ -2627,116 +2750,116 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 62278-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>6.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>4</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
         <v>4</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Rökfingersvamp
@@ -2744,491 +2867,379 @@
 Vårstarr</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 61685-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>46002</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Klasefibbla
 Tvåblad
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 21700-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 33463-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Bredgentiana
-Fältgentiana
-Slåtterfibbla</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3242,10 +3253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3259,23 +3270,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3287,52 +3298,56 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -3356,7 +3371,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3575,10 +3590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3592,23 +3607,23 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3620,56 +3635,52 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
@@ -3693,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3801,10 +3812,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44623</v>
+        <v>45428</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,25 +3827,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3849,55 +3855,55 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3911,10 +3917,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46034</v>
+        <v>45428</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,22 +3932,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3956,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3968,46 +3969,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4021,10 +4026,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45183</v>
+        <v>46099</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4036,16 +4041,11 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4066,10 +4066,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4082,42 +4082,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4127,14 +4127,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46044</v>
+        <v>44970</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,14 +4148,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -4192,42 +4192,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45947</v>
+        <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4258,20 +4258,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4295,42 +4295,42 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45981</v>
+        <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4505,10 +4505,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4521,42 +4521,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45993</v>
+        <v>45428</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4585,25 +4585,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>18.6</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4615,58 +4610,58 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4676,14 +4671,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45999</v>
+        <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4696,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4710,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4728,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4741,46 +4736,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4794,10 +4785,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46009</v>
+        <v>45183</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4815,13 +4806,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4848,49 +4839,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4904,10 +4895,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46099</v>
+        <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4919,20 +4910,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4944,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4960,42 +4956,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5009,10 +5005,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44970</v>
+        <v>45684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,22 +5020,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -5054,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5063,49 +5054,49 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5119,10 +5110,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,20 +5125,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5159,10 +5155,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5171,46 +5167,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5220,14 +5216,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45684</v>
+        <v>45993</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5239,17 +5235,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>18.6</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5264,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5273,49 +5274,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5325,14 +5326,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45428</v>
+        <v>45999</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5344,8 +5345,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5381,50 +5387,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5438,10 +5444,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46206</v>
+        <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5455,11 +5461,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5492,49 +5498,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5548,10 +5554,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46206</v>
+        <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,11 +5571,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>10.2</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5605,46 +5611,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5658,10 +5664,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5673,20 +5679,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5698,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5714,42 +5725,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36217-2022</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5759,14 +5770,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44803</v>
+        <v>46044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5780,17 +5791,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5814,20 +5825,52 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="W47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="Y47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36282-2022</t>
+          <t>A 36217-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5844,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5856,8 +5899,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5900,7 +5948,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 36282-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5910,14 +5958,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45196</v>
+        <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5929,13 +5977,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5978,7 +6021,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5988,14 +6031,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45309</v>
+        <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,6 +6048,11 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -6051,7 +6099,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6065,10 +6113,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45800</v>
+        <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6080,13 +6128,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6129,7 +6172,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6143,10 +6186,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45835</v>
+        <v>45161</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6164,7 +6207,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6207,7 +6250,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6221,10 +6264,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45918</v>
+        <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6242,7 +6285,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6285,7 +6328,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6299,10 +6342,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45925</v>
+        <v>44676</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6314,8 +6357,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6358,7 +6406,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6372,10 +6420,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46044</v>
+        <v>46071</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6389,11 +6437,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6436,7 +6484,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6450,10 +6498,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45715</v>
+        <v>46083</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6465,8 +6513,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6509,7 +6562,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,14 +6572,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45944</v>
+        <v>45835</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6544,7 +6597,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6587,7 +6640,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6601,10 +6654,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45944</v>
+        <v>46085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6622,7 +6675,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6665,7 +6718,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6679,10 +6732,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45309</v>
+        <v>46099</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6695,7 +6748,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6738,7 +6791,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6752,10 +6805,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45947</v>
+        <v>46122</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6769,11 +6822,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6816,7 +6869,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6830,10 +6883,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45954</v>
+        <v>44740</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6845,13 +6898,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6894,7 +6942,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6908,10 +6956,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45954</v>
+        <v>45918</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6929,7 +6977,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6972,7 +7020,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6986,10 +7034,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45958</v>
+        <v>45925</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7001,13 +7049,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7050,7 +7093,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7064,10 +7107,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45958</v>
+        <v>45819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7085,7 +7128,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7128,7 +7171,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7142,10 +7185,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45978</v>
+        <v>45944</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7163,7 +7206,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7206,7 +7249,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7220,10 +7263,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46071</v>
+        <v>45944</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7241,7 +7284,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7284,7 +7327,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7298,10 +7341,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45982</v>
+        <v>45174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7319,7 +7362,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7362,7 +7405,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7376,10 +7419,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46083</v>
+        <v>45947</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7397,7 +7440,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7440,7 +7483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7454,10 +7497,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45994</v>
+        <v>45309</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7470,7 +7513,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7513,7 +7556,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7523,14 +7566,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45999</v>
+        <v>45954</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7548,7 +7591,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7591,7 +7634,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7605,10 +7648,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46085</v>
+        <v>45954</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7626,7 +7669,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7669,7 +7712,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7683,10 +7726,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45958</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7700,11 +7743,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7747,7 +7790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7761,10 +7804,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45958</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7778,11 +7821,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7825,7 +7868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7835,14 +7878,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46009</v>
+        <v>45978</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7860,7 +7903,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7903,7 +7946,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7917,10 +7960,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46010</v>
+        <v>45982</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7938,7 +7981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7981,7 +8024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7995,10 +8038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46003</v>
+        <v>46247</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,11 +8055,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8059,7 +8102,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8073,10 +8116,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45013</v>
+        <v>46206</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8088,8 +8131,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8132,7 +8180,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8146,10 +8194,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46099</v>
+        <v>46206</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8161,8 +8209,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8205,7 +8258,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8219,10 +8272,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46122</v>
+        <v>46255</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8240,7 +8293,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8283,7 +8336,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8293,14 +8346,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44803</v>
+        <v>45994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8312,13 +8365,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8361,7 +8409,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8371,14 +8419,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45819</v>
+        <v>45999</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8396,7 +8444,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8439,7 +8487,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8453,10 +8501,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44676</v>
+        <v>46261</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8470,11 +8518,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8517,7 +8565,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8531,10 +8579,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45161</v>
+        <v>45196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8552,7 +8600,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8595,7 +8643,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8609,10 +8657,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45576</v>
+        <v>46002</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8626,11 +8674,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8673,7 +8721,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8687,10 +8735,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45561</v>
+        <v>46002</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8704,11 +8752,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8751,7 +8799,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8765,10 +8813,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44740</v>
+        <v>46010</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8780,8 +8828,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8824,7 +8877,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8838,10 +8891,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46247</v>
+        <v>46003</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8855,11 +8908,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8902,7 +8955,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8916,10 +8969,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>45174</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8933,11 +8986,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8980,7 +9033,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8994,10 +9047,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46206</v>
+        <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9011,11 +9064,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9058,7 +9111,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9072,10 +9125,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46255</v>
+        <v>46044</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9093,7 +9146,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9136,7 +9189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9150,10 +9203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45174</v>
+        <v>45013</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9165,13 +9218,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9214,7 +9262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9228,10 +9276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46261</v>
+        <v>45715</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9241,11 +9289,6 @@
       <c r="G92" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -9292,7 +9335,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9306,10 +9349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45174</v>
+        <v>45800</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9327,7 +9370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE93"/>
+  <dimension ref="A1:AE95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21700-2024</t>
+          <t>A 61685-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45442</v>
+        <v>46002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,14 +2934,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -2950,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2974,265 +2974,265 @@
         <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
         <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45428</v>
+        <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,20 +3827,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3855,55 +3860,55 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3917,10 +3922,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45428</v>
+        <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3932,8 +3937,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3942,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3957,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3969,50 +3979,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4026,10 +4032,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46099</v>
+        <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4042,10 +4048,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4054,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4066,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4078,39 +4084,43 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
@@ -4134,7 +4144,7 @@
         <v>44970</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4227,7 +4237,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4241,10 +4251,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44623</v>
+        <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4258,20 +4268,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4286,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4295,49 +4305,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4351,10 +4361,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44533</v>
+        <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4366,8 +4376,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4379,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4391,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4403,50 +4418,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4456,14 +4467,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45947</v>
+        <v>45993</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,13 +4492,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>18.6</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4514,49 +4525,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4566,14 +4577,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45428</v>
+        <v>45999</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4585,20 +4596,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>5.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4613,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4626,42 +4642,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4675,10 +4695,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45981</v>
+        <v>46009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4696,19 +4716,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4720,58 +4740,58 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4785,10 +4805,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45183</v>
+        <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4806,13 +4826,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4842,46 +4862,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4895,10 +4915,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46206</v>
+        <v>46034</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,14 +4932,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -4956,42 +4976,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5001,14 +5021,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45684</v>
+        <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5021,19 +5041,19 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5048,55 +5068,55 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5106,14 +5126,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46206</v>
+        <v>45684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5125,22 +5145,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5155,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5164,49 +5179,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5216,14 +5231,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45993</v>
+        <v>46044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,11 +5252,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>18.6</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5274,49 +5289,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5326,14 +5341,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45999</v>
+        <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5345,13 +5360,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5387,50 +5397,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5444,10 +5454,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46009</v>
+        <v>46099</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5459,25 +5469,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5489,58 +5494,58 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5554,10 +5559,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46009</v>
+        <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,11 +5576,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.2</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5611,46 +5616,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46034</v>
+        <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5681,14 +5686,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -5725,42 +5730,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5774,10 +5779,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46044</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5789,25 +5794,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5819,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5835,35 +5835,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44803</v>
+        <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45161</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6201,13 +6201,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6250,7 +6245,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6264,10 +6259,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45576</v>
+        <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6279,13 +6274,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6328,7 +6318,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6342,10 +6332,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44676</v>
+        <v>45819</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6363,7 +6353,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6406,7 +6396,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6420,10 +6410,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46071</v>
+        <v>45918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6441,7 +6431,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6484,7 +6474,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6498,10 +6488,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46083</v>
+        <v>45013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6513,13 +6503,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6562,7 +6547,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6576,10 +6561,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45835</v>
+        <v>45925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6591,13 +6576,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6640,7 +6620,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6650,14 +6630,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46085</v>
+        <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6675,7 +6655,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6718,7 +6698,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6732,10 +6712,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46099</v>
+        <v>45944</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6747,8 +6727,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6791,7 +6776,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6805,10 +6790,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46122</v>
+        <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6822,11 +6807,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6869,7 +6854,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6883,10 +6868,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44740</v>
+        <v>45954</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6898,8 +6883,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6942,7 +6932,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6956,10 +6946,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45918</v>
+        <v>45954</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6977,7 +6967,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7020,7 +7010,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7030,14 +7020,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45925</v>
+        <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,8 +7039,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7093,7 +7088,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7107,10 +7102,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45819</v>
+        <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7128,7 +7123,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7171,7 +7166,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7181,14 +7176,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45944</v>
+        <v>45958</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7206,7 +7201,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7249,7 +7244,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7259,14 +7254,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45944</v>
+        <v>45978</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7284,7 +7279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7327,7 +7322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7341,10 +7336,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45174</v>
+        <v>45982</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7362,7 +7357,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7405,7 +7400,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7419,10 +7414,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45947</v>
+        <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7440,7 +7435,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7483,7 +7478,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7497,10 +7492,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45309</v>
+        <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7513,7 +7508,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7556,7 +7551,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7566,14 +7561,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45954</v>
+        <v>45999</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7591,7 +7586,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7634,7 +7629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7648,10 +7643,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45954</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7665,11 +7660,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7712,7 +7707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45958</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7743,11 +7738,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7790,7 +7785,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7804,10 +7799,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45958</v>
+        <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7825,7 +7820,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7868,7 +7863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7878,14 +7873,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45978</v>
+        <v>46003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7903,7 +7898,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7946,7 +7941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7960,10 +7955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45982</v>
+        <v>45161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7981,7 +7976,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8024,7 +8019,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8038,10 +8033,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46247</v>
+        <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8059,7 +8054,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8102,7 +8097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8116,10 +8111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46206</v>
+        <v>45576</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8133,11 +8128,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8180,7 +8175,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8194,10 +8189,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46206</v>
+        <v>45561</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8211,11 +8206,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8258,7 +8253,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8272,10 +8267,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46255</v>
+        <v>46071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8289,11 +8284,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8336,7 +8331,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8350,10 +8345,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45994</v>
+        <v>46083</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8365,8 +8360,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8419,14 +8419,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45999</v>
+        <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8487,7 +8487,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46261</v>
+        <v>46099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8516,13 +8516,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8565,7 +8560,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8579,10 +8574,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45196</v>
+        <v>44740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8594,13 +8589,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8643,7 +8633,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8657,10 +8647,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46002</v>
+        <v>46122</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8678,7 +8668,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8721,7 +8711,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8735,10 +8725,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46002</v>
+        <v>46247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8756,7 +8746,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8799,7 +8789,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8813,10 +8803,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46010</v>
+        <v>45174</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8834,7 +8824,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8877,7 +8867,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8891,10 +8881,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46003</v>
+        <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8908,11 +8898,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8955,7 +8945,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8969,10 +8959,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45174</v>
+        <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8986,11 +8976,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9033,7 +9023,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9047,10 +9037,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45561</v>
+        <v>46255</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9064,11 +9054,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9111,7 +9101,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9125,10 +9115,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46044</v>
+        <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9146,7 +9136,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9189,7 +9179,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9203,10 +9193,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45013</v>
+        <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9218,8 +9208,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9262,7 +9257,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9276,10 +9271,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45715</v>
+        <v>46283</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9291,8 +9286,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9332,83 +9332,239 @@
       </c>
       <c r="V92" s="2" t="inlineStr"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
+          <t>A 38617-2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>A 25330-2025</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n">
+      <c r="D94" s="1" t="n">
         <v>45800</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F93" t="inlineStr">
+      <c r="E94" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I93" t="n">
+      <c r="I94" t="n">
         <v>5</v>
       </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="2" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>A 32187-2025</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45442</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44970</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45993</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45999</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>46034</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46044</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46099</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45819</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45918</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45925</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45944</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45947</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>45954</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>45954</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45958</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>45978</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>45982</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45999</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>46010</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>46003</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45576</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45561</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>46071</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>46083</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>46099</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44740</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>46122</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>46247</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45174</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>46255</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>46283</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>46283</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45800</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45835</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>46002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45442</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44970</v>
+        <v>45947</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4202,42 +4202,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45947</v>
+        <v>44970</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4272,13 +4272,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4312,35 +4312,35 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
         <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45993</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45999</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>46034</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45428</v>
+        <v>46044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5040,20 +5040,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5065,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5077,46 +5082,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5126,14 +5131,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45684</v>
+        <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5151,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5155,10 +5160,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5173,55 +5178,55 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5235,10 +5240,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46044</v>
+        <v>45428</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5250,25 +5255,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5280,10 +5280,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5292,46 +5292,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45428</v>
+        <v>45684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5394,53 +5394,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5454,10 +5450,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46099</v>
+        <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5469,20 +5465,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5494,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5510,42 +5511,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5562,7 +5563,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5580,7 +5581,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5624,38 +5625,38 @@
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5669,10 +5670,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5684,22 +5685,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5714,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5726,39 +5722,43 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
         <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45819</v>
+        <v>45918</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6396,7 +6396,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45918</v>
+        <v>45925</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6425,13 +6425,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6474,7 +6469,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6488,10 +6483,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45013</v>
+        <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6503,8 +6498,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6547,7 +6547,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45925</v>
+        <v>45944</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6576,8 +6576,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6620,7 +6625,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6630,14 +6635,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
         <v>45944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6655,7 +6660,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6698,7 +6703,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6712,10 +6717,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6733,7 +6738,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6776,7 +6781,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6790,10 +6795,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6816,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6854,7 +6859,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6868,10 +6873,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45954</v>
+        <v>45013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6883,13 +6888,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>45954</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44803</v>
+        <v>45958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7088,7 +7088,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7105,7 +7105,7 @@
         <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7176,14 +7176,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45958</v>
+        <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7244,7 +7244,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7254,14 +7254,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7351,13 +7351,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7400,7 +7395,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7410,14 +7405,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44676</v>
+        <v>44803</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7435,7 +7430,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7478,7 +7473,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7488,14 +7483,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7507,8 +7502,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7561,14 +7561,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7582,11 +7582,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7629,7 +7629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7646,7 +7646,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7707,7 +7707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7738,11 +7738,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7785,7 +7785,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46010</v>
+        <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7863,7 +7863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46003</v>
+        <v>46044</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7894,11 +7894,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7941,7 +7941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45161</v>
+        <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46044</v>
+        <v>46071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8050,11 +8050,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45576</v>
+        <v>46083</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8175,7 +8175,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45561</v>
+        <v>46085</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46071</v>
+        <v>45161</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8331,7 +8331,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46083</v>
+        <v>46099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8360,13 +8360,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8409,7 +8404,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46085</v>
+        <v>46247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8440,11 +8435,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8487,7 +8482,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8501,10 +8496,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46099</v>
+        <v>45576</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8516,8 +8511,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8560,7 +8560,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44740</v>
+        <v>46122</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8589,8 +8589,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8633,7 +8638,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8647,10 +8652,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46122</v>
+        <v>45561</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8664,11 +8669,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8711,7 +8716,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8725,10 +8730,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46247</v>
+        <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8746,7 +8751,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8789,7 +8794,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8803,10 +8808,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45174</v>
+        <v>46206</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8820,11 +8825,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8867,7 +8872,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8881,10 +8886,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46206</v>
+        <v>46255</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8902,7 +8907,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8945,7 +8950,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8959,10 +8964,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>44740</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8974,13 +8979,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9023,7 +9023,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9115,10 +9115,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9132,11 +9132,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45174</v>
+        <v>46283</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9274,7 +9274,7 @@
         <v>46283</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46283</v>
+        <v>45174</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9430,7 +9430,7 @@
         <v>45800</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45835</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 51149-2025</t>
+          <t>A 27330-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45947</v>
+        <v>45812</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1209,21 +1209,142 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
       </c>
       <c r="T6" t="n">
+        <v>13</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp
+Bredbrämad bastardsvärmare
+Frygisk spindling
+Grangråticka
+Kopparspindling
+Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Tvillingspindling
+Rosenticka
+Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 51149-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
         <v>19</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>19</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderdoftande fingersvamp
 Svart taggsvamp
@@ -1239,153 +1360,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 27330-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45812</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>12</v>
-      </c>
-      <c r="T7" t="n">
-        <v>13</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp
-Bredbrämad bastardsvärmare
-Frygisk spindling
-Grangråticka
-Kopparspindling
-Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Tvillingspindling
-Rosenticka
-Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 61685-2025</t>
+          <t>A 21700-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46002</v>
+        <v>45442</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,38 +2934,38 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2974,272 +2974,272 @@
         <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Klasefibbla
 Tvåblad
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 21700-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45985</v>
+        <v>45748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,23 +3270,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3298,63 +3298,59 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3368,10 +3364,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46044</v>
+        <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3385,14 +3381,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12.2</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -3425,47 +3421,51 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3482,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>12.2</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3536,47 +3536,47 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45748</v>
+        <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,20 +3607,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3644,43 +3644,43 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3808,14 +3808,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44623</v>
+        <v>44970</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3829,20 +3829,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3866,49 +3866,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45183</v>
+        <v>44623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3939,20 +3939,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3976,42 +3976,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45947</v>
+        <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,13 +4156,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4174,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4186,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4198,46 +4193,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4247,14 +4242,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44970</v>
+        <v>45428</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4266,25 +4261,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4296,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4312,42 +4302,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4361,10 +4351,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45981</v>
+        <v>45947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,7 +4372,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4394,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4406,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4422,42 +4412,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4467,14 +4457,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45993</v>
+        <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4486,22 +4476,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>18.6</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4516,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4525,49 +4510,53 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4577,14 +4566,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45999</v>
+        <v>45183</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4591,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4611,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4626,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4642,46 +4631,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4691,14 +4676,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46009</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4710,22 +4695,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4740,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4756,42 +4736,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4805,10 +4785,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46009</v>
+        <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4826,19 +4806,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4850,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4862,46 +4842,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4911,14 +4891,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46034</v>
+        <v>45993</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4936,10 +4916,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>18.6</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -4969,49 +4949,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5021,14 +5001,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46044</v>
+        <v>45999</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5042,20 +5022,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -5070,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5086,42 +5066,46 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5135,10 +5119,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46099</v>
+        <v>46034</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,20 +5134,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5175,10 +5164,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5191,42 +5180,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5240,10 +5229,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45428</v>
+        <v>46009</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5255,20 +5244,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5280,58 +5274,58 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5341,14 +5335,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45684</v>
+        <v>46044</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,17 +5354,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5385,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5394,49 +5393,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5450,10 +5449,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46206</v>
+        <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5467,11 +5466,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>10.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5507,46 +5506,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5560,10 +5559,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46206</v>
+        <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5575,25 +5574,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5605,10 +5599,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5621,42 +5615,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5670,10 +5664,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5685,17 +5679,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5710,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5722,50 +5721,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5779,10 +5774,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5794,20 +5789,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5819,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5835,35 +5835,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45196</v>
+        <v>44740</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6050,13 +6050,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6099,7 +6094,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6109,14 +6104,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,6 +6121,11 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -6172,7 +6172,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>45800</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6201,8 +6201,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6245,7 +6250,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6259,10 +6264,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45715</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6275,7 +6280,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6335,7 +6340,7 @@
         <v>45918</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6396,7 +6401,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6410,10 +6415,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45925</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6425,8 +6430,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6469,7 +6479,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6483,10 +6493,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45819</v>
+        <v>45925</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6498,13 +6508,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6547,7 +6552,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6557,14 +6562,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45944</v>
+        <v>45174</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6582,7 +6587,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6625,7 +6630,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6639,10 +6644,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45944</v>
+        <v>45309</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6654,13 +6659,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45954</v>
+        <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6859,7 +6859,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45013</v>
+        <v>45576</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6888,8 +6888,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6932,7 +6937,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6946,10 +6951,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45954</v>
+        <v>44676</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6967,7 +6972,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7010,7 +7015,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7024,10 +7029,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45958</v>
+        <v>45947</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7045,7 +7050,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7088,7 +7093,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7102,10 +7107,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7123,7 +7128,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7166,7 +7171,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7176,14 +7181,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45978</v>
+        <v>45954</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7201,7 +7206,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7244,7 +7249,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7258,10 +7263,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45982</v>
+        <v>45958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7279,7 +7284,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7322,7 +7327,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7336,10 +7341,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45994</v>
+        <v>45958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7351,8 +7356,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7395,7 +7405,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7405,14 +7415,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44803</v>
+        <v>45978</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7430,7 +7440,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7473,7 +7483,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7483,14 +7493,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45999</v>
+        <v>45982</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7508,7 +7518,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7551,7 +7561,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7565,10 +7575,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7580,13 +7590,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7629,7 +7634,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7639,14 +7644,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>45999</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7660,11 +7665,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7707,7 +7712,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7721,10 +7726,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7738,7 +7743,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -7785,7 +7790,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7799,10 +7804,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7816,11 +7821,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7863,7 +7868,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7877,10 +7882,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46044</v>
+        <v>45835</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7894,11 +7899,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7941,7 +7946,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7955,10 +7960,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44676</v>
+        <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7976,7 +7981,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8019,7 +8024,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8033,10 +8038,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46071</v>
+        <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8050,11 +8055,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8097,7 +8102,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8111,10 +8116,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46083</v>
+        <v>46010</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8132,7 +8137,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8175,7 +8180,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8189,10 +8194,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46085</v>
+        <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8210,7 +8215,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8253,7 +8258,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8267,10 +8272,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45161</v>
+        <v>46283</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8293,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8331,7 +8336,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8345,10 +8350,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46099</v>
+        <v>46283</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8360,8 +8365,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8404,7 +8414,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8418,10 +8428,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46247</v>
+        <v>46071</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8435,11 +8445,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8482,7 +8492,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8496,10 +8506,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45576</v>
+        <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8517,7 +8527,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8560,7 +8570,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8574,10 +8584,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46122</v>
+        <v>46083</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8591,11 +8601,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8638,7 +8648,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8652,10 +8662,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45561</v>
+        <v>46085</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8673,7 +8683,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8716,7 +8726,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8730,10 +8740,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46206</v>
+        <v>45561</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8747,11 +8757,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8794,7 +8804,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8808,10 +8818,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46206</v>
+        <v>46099</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8823,13 +8833,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8872,7 +8877,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8886,10 +8891,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46255</v>
+        <v>46122</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8907,7 +8912,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8950,7 +8955,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8964,10 +8969,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44740</v>
+        <v>45013</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8980,7 +8985,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9023,7 +9028,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9037,10 +9042,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46261</v>
+        <v>45819</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9054,11 +9059,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9101,7 +9106,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9115,10 +9120,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45174</v>
+        <v>45715</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9130,13 +9135,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46283</v>
+        <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46283</v>
+        <v>46206</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9288,11 +9288,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45174</v>
+        <v>46206</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9366,11 +9366,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45800</v>
+        <v>46255</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9444,11 +9444,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9491,7 +9491,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45835</v>
+        <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9522,11 +9522,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 27330-2025</t>
+          <t>A 51149-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45812</v>
+        <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1209,21 +1209,142 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
       </c>
       <c r="T6" t="n">
+        <v>19</v>
+      </c>
+      <c r="U6" t="n">
+        <v>19</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp
+Svart taggsvamp
+Ullticka
+Vårärt
+Guldlockmossa
+Mindre märgborre
+Mörk husmossa
+Platt fjädermossa
+Skogsknipprot
+Stubbspretmossa
+Tibast
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 27330-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45812</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
         <v>13</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>8</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bitter taggsvamp
 Bredbrämad bastardsvärmare
@@ -1239,153 +1360,32 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 27330-2025 artfynd.xlsx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 27330-2025 karta.png", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 27330-2025 georefererad karta.tif", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 27330-2025 FSC-klagomål.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 27330-2025 FSC-klagomål mail.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 27330-2025 tillsynsbegäran.docx", "A 27330-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 27330-2025 tillsynsbegäran mail.docx", "A 27330-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 51149-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>12</v>
-      </c>
-      <c r="T7" t="n">
-        <v>19</v>
-      </c>
-      <c r="U7" t="n">
-        <v>19</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderdoftande fingersvamp
-Svart taggsvamp
-Ullticka
-Vårärt
-Guldlockmossa
-Mindre märgborre
-Mörk husmossa
-Platt fjädermossa
-Skogsknipprot
-Stubbspretmossa
-Tibast
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21700-2024</t>
+          <t>A 61685-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45442</v>
+        <v>46002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,14 +2934,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -2950,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2974,272 +2974,272 @@
         <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,23 +3270,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3298,59 +3298,63 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3364,10 +3368,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,14 +3385,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -3421,51 +3425,47 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3482,7 +3482,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.2</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3536,47 +3536,47 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46044</v>
+        <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3644,43 +3644,43 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
         <v>45369</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3808,14 +3808,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44970</v>
+        <v>44623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3829,20 +3829,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3866,49 +3866,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44623</v>
+        <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3939,20 +3939,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3976,42 +3976,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45428</v>
+        <v>45947</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,8 +4156,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4169,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4181,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4193,46 +4198,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4242,14 +4247,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45428</v>
+        <v>44970</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,20 +4266,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4286,10 +4296,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4302,42 +4312,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4351,10 +4361,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45947</v>
+        <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4382,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4384,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4396,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4412,42 +4422,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 59993-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4457,14 +4467,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45428</v>
+        <v>45993</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,17 +4486,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>18.6</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4501,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4510,53 +4525,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 60829-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4566,14 +4577,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45183</v>
+        <v>45999</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4591,7 +4602,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4600,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4615,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4631,42 +4642,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4676,14 +4691,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>46009</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4695,17 +4710,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4720,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4736,42 +4756,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4785,10 +4805,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45981</v>
+        <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4806,19 +4826,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4830,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4842,46 +4862,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4891,14 +4911,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45993</v>
+        <v>46034</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4916,10 +4936,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>18.6</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -4949,49 +4969,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5001,14 +5021,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45999</v>
+        <v>46044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,20 +5042,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -5050,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5066,46 +5086,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5119,10 +5135,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46034</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,25 +5150,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5164,10 +5175,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5176,46 +5187,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5225,14 +5236,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46009</v>
+        <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5244,22 +5255,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5274,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5290,42 +5296,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5339,10 +5345,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46044</v>
+        <v>46099</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5354,25 +5360,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5384,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5400,42 +5401,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5449,10 +5450,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46009</v>
+        <v>45428</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5464,22 +5465,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5494,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5510,42 +5506,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46099</v>
+        <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5574,20 +5574,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5599,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5615,42 +5620,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5667,7 +5672,7 @@
         <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5685,7 +5690,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5729,38 +5734,38 @@
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5774,10 +5779,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5789,25 +5794,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5819,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5835,35 +5835,35 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44740</v>
+        <v>45196</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6050,8 +6050,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6094,7 +6099,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6104,14 +6109,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44803</v>
+        <v>45309</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6121,11 +6126,6 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -6172,7 +6172,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45800</v>
+        <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6201,13 +6201,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6250,7 +6245,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6264,10 +6259,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>45715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6280,7 +6275,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6340,7 +6335,7 @@
         <v>45918</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6401,7 +6396,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6415,10 +6410,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>45925</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6430,13 +6425,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6479,7 +6469,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6489,14 +6479,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45925</v>
+        <v>45944</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6508,8 +6498,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6552,7 +6547,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6566,10 +6561,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45174</v>
+        <v>45944</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6587,7 +6582,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6630,7 +6625,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6644,10 +6639,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45309</v>
+        <v>45947</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6659,8 +6654,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6703,7 +6703,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45944</v>
+        <v>45013</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6732,13 +6732,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6781,7 +6776,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6795,10 +6790,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6816,7 +6811,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6859,7 +6854,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6873,10 +6868,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45576</v>
+        <v>45954</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6894,7 +6889,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6937,7 +6932,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6951,10 +6946,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44676</v>
+        <v>45819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6972,7 +6967,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7015,7 +7010,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7029,10 +7024,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45947</v>
+        <v>45958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7050,7 +7045,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7093,7 +7088,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7107,10 +7102,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7128,7 +7123,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7171,7 +7166,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7181,14 +7176,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45954</v>
+        <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7206,7 +7201,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7249,7 +7244,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7263,10 +7258,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45958</v>
+        <v>45982</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7284,7 +7279,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7327,7 +7322,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7337,14 +7332,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45958</v>
+        <v>44803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7362,7 +7357,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7405,7 +7400,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7415,14 +7410,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7434,13 +7429,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7483,7 +7473,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7493,14 +7483,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45982</v>
+        <v>45999</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7518,7 +7508,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7561,7 +7551,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7575,10 +7565,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7590,8 +7580,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7634,7 +7629,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7644,14 +7639,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7665,11 +7660,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7712,7 +7707,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7743,7 +7738,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -7790,7 +7785,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7804,10 +7799,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7821,11 +7816,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7868,7 +7863,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7882,10 +7877,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45835</v>
+        <v>44676</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7903,7 +7898,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7946,7 +7941,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7960,10 +7955,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45196</v>
+        <v>46044</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7977,11 +7972,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8024,7 +8019,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8038,10 +8033,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46044</v>
+        <v>46071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8055,11 +8050,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8102,7 +8097,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8116,10 +8111,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46010</v>
+        <v>45161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8137,7 +8132,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8180,7 +8175,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8194,10 +8189,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46003</v>
+        <v>46083</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8210,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8258,7 +8253,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8272,10 +8267,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46283</v>
+        <v>46085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8293,7 +8288,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8336,7 +8331,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8350,10 +8345,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46283</v>
+        <v>46099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8365,13 +8360,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8414,7 +8404,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8428,10 +8418,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46071</v>
+        <v>45576</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8449,7 +8439,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8492,7 +8482,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8506,10 +8496,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45174</v>
+        <v>46122</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8523,11 +8513,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8570,7 +8560,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8584,10 +8574,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46083</v>
+        <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8605,7 +8595,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8648,7 +8638,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8662,10 +8652,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46085</v>
+        <v>44740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8677,13 +8667,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8726,7 +8711,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 30238-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8740,10 +8725,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45561</v>
+        <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8757,11 +8742,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8804,7 +8789,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8818,10 +8803,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46099</v>
+        <v>46206</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8833,8 +8818,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8877,7 +8867,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8891,10 +8881,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46122</v>
+        <v>46255</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8912,7 +8902,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8955,7 +8945,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8969,10 +8959,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45013</v>
+        <v>46261</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8984,8 +8974,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9028,7 +9023,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9042,10 +9037,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45819</v>
+        <v>45174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9063,7 +9058,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9106,7 +9101,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9120,10 +9115,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45715</v>
+        <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,8 +9130,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9193,10 +9193,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46247</v>
+        <v>46283</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46206</v>
+        <v>46283</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9288,11 +9288,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46206</v>
+        <v>46247</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46255</v>
+        <v>45800</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9444,11 +9444,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9491,7 +9491,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46261</v>
+        <v>45835</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9522,11 +9522,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE95"/>
+  <dimension ref="A1:AE94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58480-2025</t>
+          <t>A 62278-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45985</v>
+        <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2704,17 +2704,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2737,12 +2737,129 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Rökfingersvamp
+Vanlig sandviol
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 58480-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart trolldruva
@@ -2750,722 +2867,609 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 62278-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Rökfingersvamp
-Vanlig sandviol
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
+          <t>A 59993-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>14</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Vårärt
+Skogsknipprot
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 60829-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Sparvuggla
+Vårärt
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>A 61685-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>46002</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Klasefibbla
 Tvåblad
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 21700-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 58485-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 4132-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46044</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bredgentiana
-Nästrot</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3482,7 +3486,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3500,7 +3504,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>12.2</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3512,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3524,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3536,47 +3540,47 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3590,10 +3594,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45748</v>
+        <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,20 +3611,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3635,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3644,67 +3648,67 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S 780-2024</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45369</v>
+        <v>45748</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3718,26 +3722,26 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3749,56 +3753,56 @@
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mosippa
-Motaggsvamp</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3812,10 +3816,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44623</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3829,23 +3833,23 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3860,72 +3864,77 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>S 780-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45183</v>
+        <v>45369</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3952,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3952,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3967,58 +3976,59 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mosippa
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4032,10 +4042,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44533</v>
+        <v>45428</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4058,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4060,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4072,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4088,46 +4098,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4141,10 +4147,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45947</v>
+        <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4162,13 +4168,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4202,42 +4208,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4247,14 +4253,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44970</v>
+        <v>46044</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,14 +4274,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4312,42 +4318,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4361,10 +4367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45981</v>
+        <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,13 +4382,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4391,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4409,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4418,46 +4419,50 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59993-2025</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4467,14 +4472,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45993</v>
+        <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4486,25 +4491,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>18.6</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4516,58 +4516,58 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60829-2025</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4577,14 +4577,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45999</v>
+        <v>45947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4642,46 +4642,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4695,10 +4691,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46009</v>
+        <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4716,19 +4712,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4740,58 +4736,58 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4801,14 +4797,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46009</v>
+        <v>44970</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4826,10 +4822,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -4862,46 +4858,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4915,10 +4911,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46034</v>
+        <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4936,10 +4932,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -4969,49 +4965,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5025,10 +5021,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46044</v>
+        <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5042,11 +5038,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5082,46 +5078,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5135,10 +5131,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,20 +5146,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5178,55 +5179,55 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5236,14 +5237,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45684</v>
+        <v>44533</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5256,16 +5257,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5280,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5289,49 +5290,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5345,10 +5350,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46099</v>
+        <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5361,7 +5366,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5401,42 +5406,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5450,10 +5455,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5465,17 +5470,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5490,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5502,50 +5512,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5562,7 +5568,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5580,7 +5586,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5624,38 +5630,38 @@
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5669,10 +5675,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46206</v>
+        <v>45183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5686,17 +5692,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5730,42 +5736,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5775,14 +5781,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45428</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5795,7 +5801,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5804,10 +5810,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5822,48 +5828,48 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
@@ -5887,7 +5893,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5965,7 +5971,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6021,7 +6027,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6031,14 +6037,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45196</v>
+        <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6056,7 +6062,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6099,7 +6105,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6113,10 +6119,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45309</v>
+        <v>46003</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6128,8 +6134,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6189,7 +6200,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6245,7 +6256,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6259,10 +6270,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45715</v>
+        <v>45800</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6274,8 +6285,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6318,7 +6334,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6332,10 +6348,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45918</v>
+        <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6349,11 +6365,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6396,7 +6412,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6410,10 +6426,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45925</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6425,8 +6441,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6469,7 +6490,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6479,14 +6500,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45944</v>
+        <v>45918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6504,7 +6525,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6547,7 +6568,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6561,10 +6582,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45944</v>
+        <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6582,7 +6603,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6625,7 +6646,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6639,10 +6660,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45947</v>
+        <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6654,13 +6675,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6703,7 +6719,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6717,10 +6733,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45013</v>
+        <v>45576</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6732,8 +6748,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6776,7 +6797,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6790,10 +6811,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45954</v>
+        <v>46083</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6832,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6854,7 +6875,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6868,10 +6889,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45954</v>
+        <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6889,7 +6910,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6932,7 +6953,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6946,10 +6967,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45819</v>
+        <v>46085</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7010,7 +7031,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7020,14 +7041,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45958</v>
+        <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7045,7 +7066,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7088,7 +7109,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7102,10 +7123,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45958</v>
+        <v>45944</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7123,7 +7144,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7166,7 +7187,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7176,14 +7197,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45978</v>
+        <v>46099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7195,13 +7216,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7244,7 +7260,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7258,10 +7274,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45982</v>
+        <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7279,7 +7295,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7322,7 +7338,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7332,14 +7348,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44803</v>
+        <v>45954</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7357,7 +7373,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7400,7 +7416,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7414,10 +7430,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45994</v>
+        <v>45954</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7427,6 +7443,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -7473,7 +7494,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7483,14 +7504,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45999</v>
+        <v>45958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7508,7 +7529,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7551,7 +7572,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7565,10 +7586,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46002</v>
+        <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7582,11 +7603,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7629,7 +7650,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7643,10 +7664,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>46122</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7664,7 +7685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7707,7 +7728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7717,14 +7738,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46010</v>
+        <v>45978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7742,7 +7763,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7785,7 +7806,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7799,10 +7820,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46003</v>
+        <v>45982</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7820,7 +7841,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7863,7 +7884,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7877,10 +7898,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44676</v>
+        <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7892,13 +7913,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7941,7 +7957,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7951,14 +7967,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46044</v>
+        <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7972,11 +7988,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8019,7 +8035,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8033,10 +8049,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46071</v>
+        <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8048,13 +8064,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8097,7 +8108,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8111,10 +8122,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45161</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8128,11 +8139,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8175,7 +8186,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8189,10 +8200,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46083</v>
+        <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8206,11 +8217,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8253,7 +8264,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8267,10 +8278,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46085</v>
+        <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8299,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8331,7 +8342,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8345,10 +8356,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46099</v>
+        <v>45819</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8360,8 +8371,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8404,7 +8420,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8418,10 +8434,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45576</v>
+        <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8439,7 +8455,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8482,7 +8498,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8496,10 +8512,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46122</v>
+        <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8513,11 +8529,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8560,7 +8576,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8574,10 +8590,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45561</v>
+        <v>45309</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8589,13 +8605,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8638,7 +8649,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8652,10 +8663,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44740</v>
+        <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8667,8 +8678,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8711,7 +8727,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30238-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8725,10 +8741,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46206</v>
+        <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8746,7 +8762,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8789,7 +8805,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8803,10 +8819,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46206</v>
+        <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8824,7 +8840,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8867,7 +8883,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8881,10 +8897,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46255</v>
+        <v>45196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8898,11 +8914,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8945,7 +8961,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8959,10 +8975,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46261</v>
+        <v>46283</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8976,11 +8992,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9023,7 +9039,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9037,10 +9053,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45174</v>
+        <v>46283</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9058,7 +9074,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9118,7 +9134,7 @@
         <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9179,7 +9195,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9193,10 +9209,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46283</v>
+        <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9210,11 +9226,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9257,7 +9273,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9271,10 +9287,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46283</v>
+        <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9292,7 +9308,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9335,7 +9351,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9349,10 +9365,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46247</v>
+        <v>45013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9364,13 +9380,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9410,10 +9421,10 @@
       </c>
       <c r="V93" s="2" t="inlineStr"/>
     </row>
-    <row r="94" ht="15" customHeight="1">
+    <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9427,10 +9438,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45800</v>
+        <v>45715</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9442,13 +9453,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9487,84 +9493,6 @@
         <v>0</v>
       </c>
       <c r="V94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>A 32187-2025</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>45835</v>
-      </c>
-      <c r="E95" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>46002</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45748</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45369</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45428</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46044</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44970</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>44533</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>46003</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45800</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45576</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>46083</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>46085</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45944</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>46099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45954</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45954</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>46122</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45982</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45819</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>45309</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46283</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>46283</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45715</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45982</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45947</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>46002</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46044</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45748</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45369</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45428</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46044</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>44970</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>44533</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>46206</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>46003</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45309</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45800</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>46044</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>46071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45576</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>46083</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>46085</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45944</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>46099</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45947</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45954</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45954</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45958</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>46122</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45982</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44740</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45819</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>45309</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46206</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>46261</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46283</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>46283</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45715</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE94"/>
+  <dimension ref="A1:AE96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -899,24 +899,24 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S 3260-2025</t>
+          <t>A 51149-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45982</v>
+        <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,22 +934,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>82</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -958,21 +958,150 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>30</v>
+      </c>
+      <c r="U4" t="n">
+        <v>30</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Duvspindling
+Kopparspindling
+Läderdoftande fingersvamp
+Phellodon melilotinus
+Fjällig taggsvamp s.str.
+Persiljespindling
+Puderspindling
+Rödfläckig zontaggsvamp
+Svart taggsvamp
+Ullticka
+Vårärt
+Guldlockmossa
+Mindre märgborre
+Mörk husmossa
+Platt fjädermossa
+Skogsknipprot
+Stubbspretmossa
+Tibast
+Zontaggsvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S 3260-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S5" t="n">
         <v>15</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>43</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>4</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Stor bockrot
 Fältgentiana
@@ -991,116 +1120,116 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 3260-2025 artfynd.xlsx", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 3260-2025 karta.png", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 3260-2025 georefererad karta.tif", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 3260-2025 FSC-klagomål.docx", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 3260-2025 FSC-klagomål mail.docx", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 3260-2025 tillsynsbegäran.docx", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 3260-2025 tillsynsbegäran mail.docx", "S 3260-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/S 3260-2025 prioriterade fågelarter.docx", "S 3260-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 33463-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>12.4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>14</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>23</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>16</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Bredgentiana
 Fältgentiana
@@ -1118,153 +1247,32 @@
 Ormbär</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33463-2026 artfynd.xlsx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33463-2026 karta.png", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33463-2026 georefererad karta.tif", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33463-2026 FSC-klagomål.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33463-2026 FSC-klagomål mail.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33463-2026 tillsynsbegäran.docx", "A 33463-2026")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33463-2026 tillsynsbegäran mail.docx", "A 33463-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 51149-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>19</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Läderdoftande fingersvamp
-Svart taggsvamp
-Ullticka
-Vårärt
-Guldlockmossa
-Mindre märgborre
-Mörk husmossa
-Platt fjädermossa
-Skogsknipprot
-Stubbspretmossa
-Tibast
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51149-2025 artfynd.xlsx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51149-2025 karta.png", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51149-2025 georefererad karta.tif", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51149-2025 FSC-klagomål.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51149-2025 FSC-klagomål mail.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51149-2025 tillsynsbegäran.docx", "A 51149-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51149-2025 tillsynsbegäran mail.docx", "A 51149-2025")</f>
         <v/>
       </c>
     </row>
@@ -1288,7 +1296,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1409,7 +1417,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1524,7 +1532,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1651,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1756,7 +1764,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1885,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1998,7 +2006,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2117,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2237,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2352,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2458,7 +2466,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2572,7 +2580,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2686,7 +2694,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2803,7 +2811,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2920,7 +2928,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3033,7 +3041,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3133,7 +3141,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61693-2025</t>
+          <t>A 40038-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3147,10 +3155,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46002</v>
+        <v>46293</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3164,14 +3172,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>9.199999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -3183,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3192,395 +3200,401 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>14</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Stor bockrot
+Månlåsbräken
+Nötkråka
+Nästrot</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40038-2026 artfynd.xlsx", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40038-2026 karta.png", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40038-2026 georefererad karta.tif", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40038-2026 FSC-klagomål.docx", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40038-2026 FSC-klagomål mail.docx", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40038-2026 tillsynsbegäran.docx", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40038-2026 tillsynsbegäran mail.docx", "A 40038-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 40038-2026 prioriterade fågelarter.docx", "A 40038-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
         <v>4</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>4</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vedtrappmossa
 Brandticka</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 21700-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>1.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>3</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 4132-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46044</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bredgentiana
-Nästrot</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3594,10 +3608,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46044</v>
+        <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3611,21 +3625,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3639,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3648,50 +3662,50 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3705,10 +3719,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3722,23 +3736,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3750,59 +3764,63 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3816,10 +3834,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3833,14 +3851,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -3873,68 +3891,64 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S 780-2024</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45369</v>
+        <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3948,26 +3962,26 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3976,76 +3990,76 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
         <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Mosippa
-Motaggsvamp</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>S 780-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45428</v>
+        <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4057,8 +4071,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4067,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4082,58 +4101,59 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mosippa
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4147,10 +4167,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46034</v>
+        <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4164,20 +4184,20 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4192,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4201,49 +4221,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4257,10 +4277,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46044</v>
+        <v>46009</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4274,11 +4294,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4311,49 +4331,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4367,10 +4387,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45428</v>
+        <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,17 +4402,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4407,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4423,46 +4448,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4476,10 +4497,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46099</v>
+        <v>45947</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4491,11 +4512,16 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4504,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4516,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4532,42 +4558,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4581,10 +4607,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45947</v>
+        <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,13 +4628,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4642,42 +4668,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4691,10 +4717,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45981</v>
+        <v>45183</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4736,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4752,42 +4778,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4797,14 +4823,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44970</v>
+        <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4822,19 +4848,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4846,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4862,42 +4888,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4911,10 +4937,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46009</v>
+        <v>46044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4928,11 +4954,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4965,49 +4991,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5021,10 +5047,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46009</v>
+        <v>44533</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5036,19 +5062,14 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5082,42 +5103,46 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5131,10 +5156,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44623</v>
+        <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,13 +5171,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5161,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5179,55 +5199,55 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5237,14 +5257,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44533</v>
+        <v>44970</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5256,14 +5276,19 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5293,50 +5318,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5353,7 +5374,7 @@
         <v>45428</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5366,10 +5387,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5402,46 +5423,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5451,14 +5472,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46206</v>
+        <v>45684</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5470,22 +5491,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5500,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5509,49 +5525,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5565,10 +5581,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46206</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5580,22 +5596,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5610,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5622,46 +5633,50 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5675,10 +5690,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45183</v>
+        <v>46206</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,17 +5707,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5736,42 +5751,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5781,14 +5796,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45684</v>
+        <v>46206</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5800,17 +5815,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5825,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5834,49 +5854,49 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36217-2022</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5886,14 +5906,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44803</v>
+        <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5903,11 +5923,6 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5923,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5935,26 +5950,58 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36282-2022</t>
+          <t>A 36217-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5971,7 +6018,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5983,8 +6030,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6027,7 +6079,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 36282-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6044,7 +6096,7 @@
         <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6056,13 +6108,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6105,7 +6152,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6119,10 +6166,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46003</v>
+        <v>45196</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6140,7 +6187,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6183,7 +6230,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6197,10 +6244,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45309</v>
+        <v>46002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6212,8 +6259,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6256,7 +6308,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6270,10 +6322,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45800</v>
+        <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6287,11 +6339,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6334,7 +6386,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6348,10 +6400,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46044</v>
+        <v>45309</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6363,13 +6415,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6412,7 +6459,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6426,10 +6473,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>46010</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6447,7 +6494,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6490,7 +6537,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6504,10 +6551,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45918</v>
+        <v>45800</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6525,7 +6572,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6568,7 +6615,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6582,10 +6629,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46071</v>
+        <v>45918</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6603,7 +6650,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6663,7 +6710,7 @@
         <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6719,7 +6766,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6733,10 +6780,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45576</v>
+        <v>45835</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6754,7 +6801,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6797,7 +6844,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6807,14 +6854,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46083</v>
+        <v>45944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6832,7 +6879,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6875,7 +6922,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6889,10 +6936,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44676</v>
+        <v>45944</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6910,7 +6957,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6953,7 +7000,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6967,10 +7014,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46085</v>
+        <v>46003</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6988,7 +7035,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7031,7 +7078,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7041,14 +7088,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7066,7 +7113,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7109,7 +7156,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7123,10 +7170,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7144,7 +7191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7187,7 +7234,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7201,10 +7248,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46099</v>
+        <v>45954</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7216,8 +7263,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7260,7 +7312,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7274,10 +7326,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45947</v>
+        <v>45958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7295,7 +7347,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7338,7 +7390,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7352,10 +7404,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7373,7 +7425,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7416,7 +7468,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7426,14 +7478,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45954</v>
+        <v>45978</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7451,7 +7503,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7494,7 +7546,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7508,10 +7560,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45958</v>
+        <v>45715</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7523,13 +7575,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7572,7 +7619,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7586,10 +7633,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45958</v>
+        <v>45309</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7599,11 +7646,6 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -7650,7 +7692,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7664,10 +7706,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46122</v>
+        <v>46044</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7685,7 +7727,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7728,7 +7770,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7738,14 +7780,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7763,7 +7805,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7806,7 +7848,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7820,10 +7862,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7835,13 +7877,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7884,7 +7921,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7894,14 +7931,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45994</v>
+        <v>45999</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7913,8 +7950,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7957,7 +7999,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7967,14 +8009,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45999</v>
+        <v>46071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7992,7 +8034,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8035,7 +8077,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8049,10 +8091,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44740</v>
+        <v>46083</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,8 +8106,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8108,7 +8155,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8122,10 +8169,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>46085</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8139,11 +8186,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8186,7 +8233,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8200,10 +8247,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46002</v>
+        <v>46099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8213,11 +8260,6 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -8264,7 +8306,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8278,10 +8320,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46010</v>
+        <v>45013</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8293,13 +8335,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8342,7 +8379,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8356,10 +8393,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45819</v>
+        <v>46122</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8373,11 +8410,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8420,7 +8457,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8430,14 +8467,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45835</v>
+        <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8455,7 +8492,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8498,7 +8535,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8512,10 +8549,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45174</v>
+        <v>45819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8533,7 +8570,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8576,7 +8613,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8590,10 +8627,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45309</v>
+        <v>44676</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8605,8 +8642,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8649,7 +8691,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8663,10 +8705,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46206</v>
+        <v>45161</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8680,11 +8722,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8727,7 +8769,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8741,10 +8783,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46255</v>
+        <v>45576</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8758,11 +8800,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8805,7 +8847,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8819,10 +8861,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46261</v>
+        <v>45561</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8836,11 +8878,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8883,7 +8925,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8897,10 +8939,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45196</v>
+        <v>44740</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8912,13 +8954,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8961,7 +8998,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8975,10 +9012,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46283</v>
+        <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8992,11 +9029,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9039,7 +9076,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9053,10 +9090,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46283</v>
+        <v>46255</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9070,11 +9107,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9117,7 +9154,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9134,7 +9171,7 @@
         <v>45174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9152,7 +9189,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9195,7 +9232,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9209,10 +9246,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9230,7 +9267,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9273,7 +9310,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9287,10 +9324,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45561</v>
+        <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9308,7 +9345,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9351,7 +9388,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9365,10 +9402,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45013</v>
+        <v>46283</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9380,8 +9417,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9421,10 +9463,10 @@
       </c>
       <c r="V93" s="2" t="inlineStr"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9438,61 +9480,222 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45715</v>
+        <v>46283</v>
       </c>
       <c r="E94" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>A 33485-2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>A 40057-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="E96" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="2" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45982</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>46247</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>45999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46293</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61685-2025</t>
+          <t>A 21700-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46002</v>
+        <v>45442</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3289,38 +3289,38 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3329,265 +3329,265 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 61693-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Klasefibbla
 Tvåblad
 Kärrknipprot</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 21700-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45442</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
         <v>45748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J28" t="n">
         <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -3776,51 +3776,47 @@
         <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3837,7 +3833,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3855,7 +3851,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.2</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -3867,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3879,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -3891,47 +3887,47 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3945,10 +3941,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46044</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3962,14 +3958,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -3978,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3990,10 +3986,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -4002,40 +3998,44 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
         <v>45369</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,25 +4182,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4215,55 +4210,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4277,10 +4272,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46009</v>
+        <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4331,49 +4326,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46009</v>
+        <v>46044</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4404,11 +4399,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10.2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4444,46 +4439,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45947</v>
+        <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4512,13 +4507,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4527,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4542,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4554,46 +4544,50 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4607,10 +4601,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46034</v>
+        <v>45947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4628,13 +4622,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4668,42 +4662,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4717,10 +4711,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45183</v>
+        <v>45981</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4762,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4778,42 +4772,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4823,14 +4817,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45981</v>
+        <v>44970</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4848,19 +4842,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4872,10 +4866,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4888,42 +4882,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4937,10 +4931,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46044</v>
+        <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,11 +4948,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4991,49 +4985,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5047,10 +5041,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44533</v>
+        <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5062,14 +5056,19 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>10.2</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5103,39 +5102,35 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
@@ -5159,7 +5154,7 @@
         <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5247,7 +5242,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5257,14 +5252,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44970</v>
+        <v>44623</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,20 +5273,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5306,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5315,49 +5310,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45428</v>
+        <v>44533</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5387,7 +5382,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5399,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5411,10 +5406,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5427,42 +5422,46 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5472,14 +5471,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45684</v>
+        <v>45428</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5491,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5501,10 +5500,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5519,55 +5518,55 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5581,10 +5580,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45428</v>
+        <v>45183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5596,8 +5595,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5606,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5621,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5633,50 +5637,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5686,14 +5686,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46206</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5705,22 +5705,17 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5735,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5744,49 +5739,49 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5803,7 +5798,7 @@
         <v>46206</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,7 +5816,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5865,38 +5860,38 @@
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5910,10 +5905,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45428</v>
+        <v>46206</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5925,20 +5920,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5950,10 +5950,10 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5966,35 +5966,35 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
         <v>44803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45196</v>
+        <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6230,7 +6230,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6261,11 +6261,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46002</v>
+        <v>45309</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6337,13 +6337,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6386,7 +6381,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6400,10 +6395,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45309</v>
+        <v>45800</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6415,8 +6410,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46010</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45800</v>
+        <v>45918</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45918</v>
+        <v>45576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
         <v>45925</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45835</v>
+        <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6797,11 +6797,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6844,7 +6844,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6854,14 +6854,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45944</v>
+        <v>45835</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6936,10 +6936,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45944</v>
+        <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7000,7 +7000,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7010,14 +7010,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46003</v>
+        <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7078,7 +7078,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45954</v>
+        <v>45947</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7251,7 +7251,7 @@
         <v>45954</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>45958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7478,14 +7478,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45978</v>
+        <v>45958</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7546,7 +7546,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7556,14 +7556,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45715</v>
+        <v>45978</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7575,8 +7575,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7619,7 +7624,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7633,10 +7638,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45309</v>
+        <v>46071</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7648,8 +7653,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7692,7 +7702,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7706,10 +7716,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46044</v>
+        <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7723,11 +7733,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7770,7 +7780,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7784,10 +7794,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45982</v>
+        <v>46083</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7805,7 +7815,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7865,7 +7875,7 @@
         <v>45994</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7921,7 +7931,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7931,14 +7941,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45999</v>
+        <v>44740</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7950,13 +7960,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7999,7 +8004,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8009,14 +8014,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46071</v>
+        <v>45999</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8034,7 +8039,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8077,7 +8082,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8091,10 +8096,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8155,7 +8160,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8169,10 +8174,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46085</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8186,11 +8191,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8233,7 +8238,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8247,10 +8252,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46099</v>
+        <v>46002</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8260,6 +8265,11 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -8306,7 +8316,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8320,10 +8330,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45013</v>
+        <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8335,8 +8345,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8379,7 +8394,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8393,10 +8408,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46122</v>
+        <v>46099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8408,13 +8423,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8457,7 +8467,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8467,14 +8477,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44803</v>
+        <v>46122</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8488,11 +8498,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8535,7 +8545,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8549,10 +8559,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45819</v>
+        <v>45174</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8570,7 +8580,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8613,7 +8623,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8627,10 +8637,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44676</v>
+        <v>45309</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8642,13 +8652,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8691,7 +8696,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8705,10 +8710,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45161</v>
+        <v>45819</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8726,7 +8731,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8769,7 +8774,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8783,10 +8788,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45576</v>
+        <v>45196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8804,7 +8809,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8847,7 +8852,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8861,10 +8866,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45561</v>
+        <v>45174</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8882,7 +8887,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8925,7 +8930,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8939,10 +8944,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44740</v>
+        <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8954,8 +8959,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8998,7 +9008,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9012,10 +9022,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9029,11 +9039,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9093,7 +9103,7 @@
         <v>46255</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9154,7 +9164,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9168,10 +9178,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45174</v>
+        <v>46261</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9185,11 +9195,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9232,7 +9242,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9246,10 +9256,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46261</v>
+        <v>45013</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9261,13 +9271,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9310,7 +9315,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9324,10 +9329,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45174</v>
+        <v>46283</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9345,7 +9350,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9388,7 +9393,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9405,7 +9410,7 @@
         <v>46283</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9423,7 +9428,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9466,7 +9471,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9480,10 +9485,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46283</v>
+        <v>45715</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9495,13 +9500,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9561,7 +9561,7 @@
         <v>46247</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>46293</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45982</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>46247</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 62278-2025</t>
+          <t>A 58480-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46006</v>
+        <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2745,12 +2745,359 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
+        <v>9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Svart trolldruva
+Tibast
+Vätteros</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 59993-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>14</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Vårärt
+Skogsknipprot
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 60829-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Sparvuggla
+Vårärt
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 62278-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
         <v>6</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Rökfingersvamp
@@ -2758,383 +3105,36 @@
 Vårstarr</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 58480-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Svart trolldruva
-Tibast
-Vätteros</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 59993-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>14</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Vårärt
-Skogsknipprot
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 60829-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Sparvuggla
-Vårärt
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>46293</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3258,454 +3258,456 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
+          <t>A 40476-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Platt spretmossa
+Vedtrappmossa
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40476-2026 artfynd.xlsx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40476-2026 karta.png", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40476-2026 georefererad karta.tif", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40476-2026 FSC-klagomål.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40476-2026 FSC-klagomål mail.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40476-2026 tillsynsbegäran.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40476-2026 tillsynsbegäran mail.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>A 21700-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>1.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 61693-2025</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>46002</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>4</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Vedtrappmossa
 Brandticka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 15739-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45748</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>7</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3719,10 +3721,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46044</v>
+        <v>45748</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3736,23 +3738,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3764,59 +3766,59 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3830,10 +3832,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46044</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,14 +3849,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -3863,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3875,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -3887,47 +3889,51 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3941,10 +3947,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3958,14 +3964,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J30" t="n">
         <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -3998,68 +4004,64 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S 780-2024</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45369</v>
+        <v>46044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4073,26 +4075,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4101,59 +4103,59 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mosippa
-Motaggsvamp</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 40478-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4167,10 +4169,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45428</v>
+        <v>46295</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4182,20 +4184,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4207,75 +4214,80 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Rödgul trumpetsvamp
+Järpe</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40478-2026 artfynd.xlsx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40478-2026 karta.png", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40478-2026 georefererad karta.tif", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40478-2026 FSC-klagomål.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40478-2026 FSC-klagomål mail.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40478-2026 tillsynsbegäran.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40478-2026 tillsynsbegäran mail.docx", "A 40478-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 40478-2026 prioriterade fågelarter.docx", "A 40478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>S 780-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46034</v>
+        <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4293,22 +4305,22 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4317,58 +4329,59 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mosippa
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4382,10 +4395,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46044</v>
+        <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4399,17 +4412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4443,42 +4456,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4492,10 +4505,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45428</v>
+        <v>44533</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4508,7 +4521,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4517,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4532,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4548,46 +4561,46 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4601,10 +4614,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45947</v>
+        <v>45428</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4616,13 +4629,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4634,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4646,10 +4654,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4658,46 +4666,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4707,14 +4715,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45981</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,25 +4734,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4759,55 +4762,55 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4817,14 +4820,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44970</v>
+        <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,20 +4841,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4866,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4875,49 +4878,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4931,10 +4934,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46009</v>
+        <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4946,25 +4949,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4976,58 +4974,58 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5037,14 +5035,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46009</v>
+        <v>44970</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5062,10 +5060,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>10.2</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -5098,46 +5096,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5151,10 +5149,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46099</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5167,19 +5165,19 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5194,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5203,46 +5201,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5256,10 +5258,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44623</v>
+        <v>45947</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,20 +5275,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5301,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5310,49 +5312,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5366,10 +5368,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44533</v>
+        <v>45981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5381,8 +5383,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5394,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5406,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5418,50 +5425,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5475,10 +5478,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45428</v>
+        <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5490,20 +5493,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5515,58 +5523,58 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5580,10 +5588,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45183</v>
+        <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5601,13 +5609,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5637,46 +5645,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5686,14 +5694,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45684</v>
+        <v>46034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5705,17 +5713,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5730,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5739,49 +5752,49 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30233-2026</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5795,10 +5808,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46206</v>
+        <v>46044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5816,7 +5829,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5860,38 +5873,38 @@
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30236-2026</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5905,10 +5918,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46206</v>
+        <v>46099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5920,25 +5933,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5950,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5966,42 +5974,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36217-2022</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6011,14 +6019,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44803</v>
+        <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6032,17 +6040,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6066,20 +6074,52 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="W49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36282-2022</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6089,14 +6129,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44803</v>
+        <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,14 +6148,19 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6139,20 +6184,52 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="W50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="Y50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 36217-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6169,7 +6246,7 @@
         <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6187,7 +6264,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6230,7 +6307,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 36282-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6240,14 +6317,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46003</v>
+        <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6259,13 +6336,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6308,7 +6380,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6322,10 +6394,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45309</v>
+        <v>44676</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6337,8 +6409,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6381,7 +6458,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6395,10 +6472,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45800</v>
+        <v>45196</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6416,7 +6493,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6459,7 +6536,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38226-2023</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6473,10 +6550,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>45174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6494,7 +6571,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6537,7 +6614,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6551,10 +6628,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45918</v>
+        <v>45715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6566,13 +6643,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6615,7 +6687,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6629,10 +6701,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45576</v>
+        <v>45309</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6644,13 +6716,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6693,7 +6760,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 38226-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6707,10 +6774,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45925</v>
+        <v>45161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6722,8 +6789,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6766,7 +6838,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6780,10 +6852,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46044</v>
+        <v>45174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6797,11 +6869,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6844,7 +6916,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6858,10 +6930,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45835</v>
+        <v>45576</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6879,7 +6951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6922,7 +6994,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6936,10 +7008,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44676</v>
+        <v>45561</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6957,7 +7029,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7000,7 +7072,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7010,14 +7082,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45944</v>
+        <v>45013</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7029,13 +7101,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7078,7 +7145,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7092,10 +7159,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45944</v>
+        <v>45309</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7107,13 +7174,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7156,7 +7218,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7170,10 +7232,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45947</v>
+        <v>44740</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7185,13 +7247,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7234,7 +7291,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7248,10 +7305,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45954</v>
+        <v>45800</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7269,7 +7326,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7312,7 +7369,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7322,14 +7379,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45954</v>
+        <v>44803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7347,7 +7404,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7390,7 +7447,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7404,10 +7461,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45958</v>
+        <v>45835</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7425,7 +7482,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7468,7 +7525,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53184-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7478,14 +7535,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45958</v>
+        <v>45944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7503,7 +7560,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7546,7 +7603,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7556,14 +7613,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45978</v>
+        <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7581,7 +7638,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7624,7 +7681,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7638,10 +7695,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46071</v>
+        <v>45947</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7659,7 +7716,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7702,7 +7759,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7716,10 +7773,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45982</v>
+        <v>45954</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7737,7 +7794,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7780,7 +7837,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7794,10 +7851,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46083</v>
+        <v>45954</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7815,7 +7872,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7858,7 +7915,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 53184-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7872,10 +7929,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45994</v>
+        <v>45958</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7887,8 +7944,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7931,7 +7993,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7945,10 +8007,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44740</v>
+        <v>45958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7960,8 +8022,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8004,7 +8071,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8014,14 +8081,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45999</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8039,7 +8106,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8082,7 +8149,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8096,10 +8163,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46085</v>
+        <v>45925</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8111,13 +8178,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8160,7 +8222,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8170,14 +8232,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>45978</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8191,11 +8253,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8238,7 +8300,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8252,10 +8314,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46002</v>
+        <v>45982</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8269,11 +8331,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8316,7 +8378,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63365-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8330,10 +8392,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46010</v>
+        <v>45994</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8345,13 +8407,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8394,7 +8451,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8404,14 +8461,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46099</v>
+        <v>45999</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8423,8 +8480,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8467,7 +8529,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8481,10 +8543,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46122</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8502,7 +8564,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8545,7 +8607,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8559,10 +8621,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45174</v>
+        <v>46002</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8576,11 +8638,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8623,7 +8685,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 63365-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8637,10 +8699,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45309</v>
+        <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8652,8 +8714,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8696,7 +8763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8710,10 +8777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45819</v>
+        <v>46003</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8731,7 +8798,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8774,7 +8841,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8788,10 +8855,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45196</v>
+        <v>46044</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8805,11 +8872,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8852,7 +8919,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8866,10 +8933,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45174</v>
+        <v>46071</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8887,7 +8954,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8930,7 +8997,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8944,10 +9011,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46206</v>
+        <v>46083</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8961,11 +9028,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9008,7 +9075,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9022,10 +9089,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45561</v>
+        <v>46085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9043,7 +9110,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9086,7 +9153,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9100,10 +9167,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46255</v>
+        <v>46099</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9115,13 +9182,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9164,7 +9226,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9178,10 +9240,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46261</v>
+        <v>46122</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9199,7 +9261,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9242,7 +9304,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9256,10 +9318,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45013</v>
+        <v>45819</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9271,8 +9333,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9315,7 +9382,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9329,10 +9396,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46283</v>
+        <v>46206</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9346,11 +9413,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9393,7 +9460,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9407,10 +9474,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46283</v>
+        <v>46255</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9424,11 +9491,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9471,7 +9538,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9485,10 +9552,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45715</v>
+        <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9498,6 +9565,11 @@
       <c r="G94" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -9544,7 +9616,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9558,10 +9630,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46247</v>
+        <v>46283</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9575,11 +9647,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9619,83 +9691,239 @@
       </c>
       <c r="V95" s="2" t="inlineStr"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
+          <t>A 33485-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>A 40057-2026</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D96" s="1" t="n">
+      <c r="D97" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="E96" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="E97" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I96" t="n">
+      <c r="I97" t="n">
         <v>1.1</v>
       </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="2" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>A 38617-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45982</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>46247</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45810</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46155</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46247</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58480-2025</t>
+          <t>A 62278-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45985</v>
+        <v>46006</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2712,17 +2712,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -2745,12 +2745,129 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Rökfingersvamp
+Vanlig sandviol
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 58480-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart trolldruva
@@ -2758,116 +2875,116 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 59993-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45993</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>18.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>14</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Vårärt
@@ -2875,112 +2992,112 @@
 Svavelriska</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 60829-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>5.5</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Sparvuggla
@@ -2988,153 +3105,36 @@
 Svavelriska</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 62278-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Rökfingersvamp
-Vanlig sandviol
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>46293</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>46295</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21700-2024</t>
+          <t>A 61693-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45442</v>
+        <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3402,11 +3402,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3433,281 +3433,281 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
       </c>
       <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Vedtrappmossa
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 21700-2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45442</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Töcknig trymal
 Skuggorangelav
 Scharlakansvårskål agg.</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 61685-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 61693-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Vedtrappmossa
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61693-2025 artfynd.xlsx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61693-2025 karta.png", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61693-2025 georefererad karta.tif", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61693-2025 FSC-klagomål.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61693-2025 FSC-klagomål mail.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61693-2025 tillsynsbegäran.docx", "A 61693-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61693-2025 tillsynsbegäran mail.docx", "A 61693-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45748</v>
+        <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3738,23 +3738,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>12.2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3766,59 +3766,59 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3849,15 +3849,15 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3877,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -3889,51 +3889,47 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3947,10 +3943,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46044</v>
+        <v>45748</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3964,23 +3960,23 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12.2</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3992,59 +3988,59 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4058,10 +4054,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46044</v>
+        <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,14 +4071,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -4091,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4103,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4115,40 +4111,44 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
         <v>46295</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45369</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4456,42 +4456,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44533</v>
+        <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4545,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4561,46 +4561,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 4131-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4614,10 +4610,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45428</v>
+        <v>46044</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4629,20 +4625,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4654,10 +4655,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4666,46 +4667,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3950-2025</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4715,14 +4716,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,10 +4736,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -4768,49 +4769,53 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4824,10 +4829,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44623</v>
+        <v>45947</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,20 +4846,20 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4869,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4878,49 +4883,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 14127-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45428</v>
+        <v>46099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4955,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4990,42 +4995,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5035,14 +5040,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44970</v>
+        <v>45981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5060,19 +5065,19 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5084,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5100,42 +5105,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5145,14 +5150,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>44970</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5164,17 +5169,22 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5189,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5201,50 +5211,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5258,10 +5264,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45947</v>
+        <v>46009</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,13 +5285,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5312,49 +5318,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 62938-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5368,10 +5374,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45981</v>
+        <v>46009</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5389,19 +5395,19 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5413,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5425,46 +5431,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5478,10 +5484,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46009</v>
+        <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5495,20 +5501,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5523,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5535,46 +5541,46 @@
         <v>4</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5588,10 +5594,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46009</v>
+        <v>44533</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,19 +5609,14 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5649,42 +5650,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 19304-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5698,10 +5703,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46034</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5713,25 +5718,20 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5743,10 +5743,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5759,42 +5759,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4131-2026</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46044</v>
+        <v>45183</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5825,17 +5825,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5869,42 +5869,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4131-2026 artfynd.xlsx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4131-2026 karta.png", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4131-2026 georefererad karta.tif", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4131-2026 FSC-klagomål.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4131-2026 FSC-klagomål mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4131-2026 tillsynsbegäran.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4131-2026 tillsynsbegäran mail.docx", "A 4131-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14127-2026</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46099</v>
+        <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5943,10 +5943,10 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5961,48 +5961,48 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 14127-2026 artfynd.xlsx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 14127-2026 karta.png", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 14127-2026 georefererad karta.tif", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 14127-2026 FSC-klagomål.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 14127-2026 FSC-klagomål mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 14127-2026 tillsynsbegäran.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 14127-2026 tillsynsbegäran mail.docx", "A 14127-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>46206</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>44803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44803</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16990-2022</t>
+          <t>A 36216-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6390,14 +6390,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44676</v>
+        <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6458,7 +6458,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46113-2023</t>
+          <t>A 61839-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45196</v>
+        <v>46003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41272-2023</t>
+          <t>A 2184-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45174</v>
+        <v>45309</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6565,13 +6565,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9533-2025</t>
+          <t>A 4134-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45715</v>
+        <v>46044</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6643,8 +6638,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6687,7 +6687,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2184-2024</t>
+          <t>A 25330-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45309</v>
+        <v>45800</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6716,8 +6716,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6777,7 +6782,7 @@
         <v>45161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41276-2023</t>
+          <t>A 45033-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6852,10 +6857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45174</v>
+        <v>45918</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6873,7 +6878,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6916,7 +6921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45372-2024</t>
+          <t>A 9394-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6930,10 +6935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45576</v>
+        <v>46071</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6951,7 +6956,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6994,7 +6999,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41929-2024</t>
+          <t>A 46510-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7008,10 +7013,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45561</v>
+        <v>45925</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7023,13 +7028,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7072,7 +7072,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 14590-2023</t>
+          <t>A 11467-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45013</v>
+        <v>46083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7101,8 +7101,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7145,7 +7150,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2183-2024</t>
+          <t>A 11848-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7159,10 +7164,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45309</v>
+        <v>46085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7174,8 +7179,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7218,7 +7228,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26815-2022</t>
+          <t>A 45372-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7232,10 +7242,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44740</v>
+        <v>45576</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7247,8 +7257,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7291,7 +7306,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25330-2025</t>
+          <t>A 50398-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7301,14 +7316,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45800</v>
+        <v>45944</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7326,7 +7341,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7369,7 +7384,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36216-2022</t>
+          <t>A 50371-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7379,14 +7394,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44803</v>
+        <v>45944</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7404,7 +7419,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7447,7 +7462,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32187-2025</t>
+          <t>A 16990-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7461,10 +7476,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45835</v>
+        <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7482,7 +7497,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7525,7 +7540,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50398-2025</t>
+          <t>A 51237-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7535,14 +7550,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7560,7 +7575,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7603,7 +7618,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50371-2025</t>
+          <t>A 14091-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7617,10 +7632,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45944</v>
+        <v>46099</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7632,13 +7647,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7681,7 +7691,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51237-2025</t>
+          <t>A 52477-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7695,10 +7705,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7716,7 +7726,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7759,7 +7769,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52477-2025</t>
+          <t>A 52498-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7776,7 +7786,7 @@
         <v>45954</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7794,7 +7804,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7837,7 +7847,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52498-2025</t>
+          <t>A 53173-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7851,10 +7861,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7872,7 +7882,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7932,7 +7942,7 @@
         <v>45958</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7993,7 +8003,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 53173-2025</t>
+          <t>A 17851-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8007,10 +8017,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45958</v>
+        <v>46122</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8024,11 +8034,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8071,7 +8081,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45033-2025</t>
+          <t>A 56861-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8081,14 +8091,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45978</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8106,7 +8116,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8149,7 +8159,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46510-2025</t>
+          <t>A 58168-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8163,10 +8173,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45925</v>
+        <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8178,8 +8188,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8222,7 +8237,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56861-2025</t>
+          <t>A 60256-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8232,14 +8247,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8251,13 +8266,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8300,7 +8310,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58168-2025</t>
+          <t>A 60842-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8310,14 +8320,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45982</v>
+        <v>45999</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8335,7 +8345,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8378,7 +8388,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60256-2025</t>
+          <t>A 61694-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8392,10 +8402,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8407,8 +8417,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8451,7 +8466,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60842-2025</t>
+          <t>A 61691-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8461,14 +8476,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8482,11 +8497,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8529,7 +8544,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61694-2025</t>
+          <t>A 26815-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8543,10 +8558,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>44740</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8558,13 +8573,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8607,7 +8617,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61691-2025</t>
+          <t>A 32187-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8621,10 +8631,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46002</v>
+        <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8638,11 +8648,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8702,7 +8712,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8763,7 +8773,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61839-2025</t>
+          <t>A 28670-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8777,10 +8787,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46003</v>
+        <v>45819</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8798,7 +8808,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8841,7 +8851,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4134-2026</t>
+          <t>A 41272-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8855,10 +8865,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46044</v>
+        <v>45174</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8872,11 +8882,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8919,7 +8929,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9394-2026</t>
+          <t>A 2183-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46071</v>
+        <v>45309</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8948,13 +8958,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8997,7 +9002,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11467-2026</t>
+          <t>A 30234-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9011,10 +9016,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46083</v>
+        <v>46206</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9028,11 +9033,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9075,7 +9080,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11848-2026</t>
+          <t>A 34575-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46085</v>
+        <v>46255</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9106,11 +9111,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9153,7 +9158,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14091-2026</t>
+          <t>A 35356-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9167,10 +9172,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46099</v>
+        <v>46261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9182,8 +9187,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9226,7 +9236,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17851-2026</t>
+          <t>A 46113-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9240,10 +9250,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46122</v>
+        <v>45196</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9257,11 +9267,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9304,7 +9314,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28670-2025</t>
+          <t>A 41276-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9318,10 +9328,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45819</v>
+        <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9339,7 +9349,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9382,7 +9392,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30234-2026</t>
+          <t>A 41929-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9396,10 +9406,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46206</v>
+        <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9413,11 +9423,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9460,7 +9470,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34575-2026</t>
+          <t>A 38636-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9474,10 +9484,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46255</v>
+        <v>46283</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9491,11 +9501,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35356-2026</t>
+          <t>A 33485-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46261</v>
+        <v>46247</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9573,7 +9583,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9616,7 +9626,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38636-2026</t>
+          <t>A 40057-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9630,10 +9640,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9651,7 +9661,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9694,7 +9704,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33485-2026</t>
+          <t>A 38617-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9708,10 +9718,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46247</v>
+        <v>46283</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9725,11 +9735,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9772,7 +9782,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40057-2026</t>
+          <t>A 14590-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9786,10 +9796,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46293</v>
+        <v>45013</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9801,13 +9811,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9850,7 +9855,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38617-2026</t>
+          <t>A 9533-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9864,10 +9869,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46283</v>
+        <v>45715</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9879,13 +9884,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>

--- a/Översikt ÄLVKARLEBY.xlsx
+++ b/Översikt ÄLVKARLEBY.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE98"/>
+  <dimension ref="A1:AE96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45635</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         <v>45828</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45947</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -940,16 +940,16 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -958,36 +958,41 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="U4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Duvspindling
+          <t>Dvärgtaggsvamp
+Duvspindling
+Gyllenspindling
 Kopparspindling
 Läderdoftande fingersvamp
 Phellodon melilotinus
 Fjällig taggsvamp s.str.
+Orange taggsvamp
 Persiljespindling
 Puderspindling
 Rödfläckig zontaggsvamp
+Skarp dropptaggsvamp
 Svart taggsvamp
 Ullticka
 Vårärt
 Guldlockmossa
 Mindre märgborre
 Mörk husmossa
+Olivspindling
 Platt fjädermossa
 Skogsknipprot
 Stubbspretmossa
@@ -1045,7 +1050,7 @@
         <v>45982</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1173,7 +1178,7 @@
         <v>46247</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1296,7 +1301,7 @@
         <v>45812</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1422,7 @@
         <v>45684</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1537,7 @@
         <v>45771</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1651,7 +1656,7 @@
         <v>45684</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1764,7 +1769,7 @@
         <v>45925</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1885,7 +1890,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2006,7 +2011,7 @@
         <v>45684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2117,7 +2122,7 @@
         <v>45638</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2220,7 +2225,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26681-2025</t>
+          <t>A 22563-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2234,10 +2239,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45810</v>
+        <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,26 +2256,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2279,136 +2284,21 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Nästrot
-Skogsknipprot
-Tibast
-Tvåblad
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 26681-2025 artfynd.xlsx", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 26681-2025 karta.png", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 26681-2025 georefererad karta.tif", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 26681-2025 FSC-klagomål.docx", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 26681-2025 FSC-klagomål mail.docx", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 26681-2025 tillsynsbegäran.docx", "A 26681-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 26681-2025 tillsynsbegäran mail.docx", "A 26681-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 22563-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄLVKARLEBY</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Backruta
 Klasefibbla
@@ -2417,112 +2307,112 @@
 Tibast</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 22563-2026 artfynd.xlsx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 22563-2026 karta.png", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 22563-2026 georefererad karta.tif", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 22563-2026 FSC-klagomål.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 22563-2026 FSC-klagomål mail.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 22563-2026 tillsynsbegäran.docx", "A 22563-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 22563-2026 tillsynsbegäran mail.docx", "A 22563-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 33464-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I16" t="n">
         <v>5.1</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T16" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skrovlig taggsvamp
 Grantaggsvamp
@@ -2531,112 +2421,112 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 33464-2026 artfynd.xlsx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 33464-2026 karta.png", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 33464-2026 georefererad karta.tif", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 33464-2026 FSC-klagomål.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 33464-2026 FSC-klagomål mail.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 33464-2026 tillsynsbegäran.docx", "A 33464-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 33464-2026 tillsynsbegäran mail.docx", "A 33464-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>S 4507-2023</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45274</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I17" t="n">
         <v>11.4</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S17" t="n">
         <v>5</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T17" t="n">
         <v>11</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Stor bockrot
 Kattunvisslare
@@ -2645,112 +2535,112 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 4507-2023 artfynd.xlsx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 4507-2023 karta.png", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 4507-2023 georefererad karta.tif", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 4507-2023 FSC-klagomål.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 4507-2023 FSC-klagomål mail.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 4507-2023 tillsynsbegäran.docx", "S 4507-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 4507-2023 tillsynsbegäran mail.docx", "S 4507-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 62278-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I18" t="n">
         <v>6.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
         <v>4</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Rökfingersvamp
@@ -2758,116 +2648,116 @@
 Vårstarr</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62278-2025 artfynd.xlsx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62278-2025 karta.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62278-2025 georefererad karta.tif", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 62278-2025 karta knärot.png", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62278-2025 FSC-klagomål.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62278-2025 FSC-klagomål mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62278-2025 tillsynsbegäran.docx", "A 62278-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62278-2025 tillsynsbegäran mail.docx", "A 62278-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 58480-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I19" t="n">
         <v>4.1</v>
       </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T19" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart trolldruva
@@ -2875,116 +2765,116 @@
 Vätteros</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58480-2025 artfynd.xlsx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58480-2025 karta.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58480-2025 georefererad karta.tif", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58480-2025 karta knärot.png", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58480-2025 FSC-klagomål.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58480-2025 FSC-klagomål mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58480-2025 tillsynsbegäran.docx", "A 58480-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58480-2025 tillsynsbegäran mail.docx", "A 58480-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 59993-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45993</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I20" t="n">
         <v>18.6</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T20" t="n">
         <v>14</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Vårärt
@@ -2992,112 +2882,112 @@
 Svavelriska</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 59993-2025 artfynd.xlsx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 59993-2025 karta.png", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 59993-2025 georefererad karta.tif", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 59993-2025 FSC-klagomål.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 59993-2025 FSC-klagomål mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 59993-2025 tillsynsbegäran.docx", "A 59993-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 59993-2025 tillsynsbegäran mail.docx", "A 59993-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 60829-2025</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I21" t="n">
         <v>5.5</v>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Sparvuggla
@@ -3105,116 +2995,116 @@
 Svavelriska</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 60829-2025 artfynd.xlsx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 60829-2025 karta.png", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 60829-2025 georefererad karta.tif", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 60829-2025 FSC-klagomål.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 60829-2025 FSC-klagomål mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 60829-2025 tillsynsbegäran.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 60829-2025 tillsynsbegäran mail.docx", "A 60829-2025")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 60829-2025 prioriterade fågelarter.docx", "A 60829-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 40038-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I22" t="n">
         <v>24.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T22" t="n">
         <v>14</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Stor bockrot
 Månlåsbräken
@@ -3222,116 +3112,116 @@
 Nästrot</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40038-2026 artfynd.xlsx", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40038-2026 karta.png", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40038-2026 georefererad karta.tif", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40038-2026 FSC-klagomål.docx", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40038-2026 FSC-klagomål mail.docx", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40038-2026 tillsynsbegäran.docx", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40038-2026 tillsynsbegäran mail.docx", "A 40038-2026")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 40038-2026 prioriterade fågelarter.docx", "A 40038-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 40476-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E23" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>UPPSALA LÄN</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Bergvik skog öst AB</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I23" t="n">
         <v>11.2</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T23" t="n">
         <v>4</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Ask
 Platt spretmossa
@@ -3339,32 +3229,144 @@
 Myskmadra</t>
         </is>
       </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40476-2026 artfynd.xlsx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40476-2026 karta.png", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40476-2026 georefererad karta.tif", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40476-2026 FSC-klagomål.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40476-2026 FSC-klagomål mail.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40476-2026 tillsynsbegäran.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40476-2026 tillsynsbegäran mail.docx", "A 40476-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 61685-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄLVKARLEBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Klasefibbla
+Tvåblad
+Kärrknipprot</t>
+        </is>
+      </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40476-2026 artfynd.xlsx", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40476-2026 karta.png", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40476-2026 georefererad karta.tif", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40476-2026 FSC-klagomål.docx", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40476-2026 FSC-klagomål mail.docx", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40476-2026 tillsynsbegäran.docx", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40476-2026 tillsynsbegäran mail.docx", "A 40476-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
         <v/>
       </c>
     </row>
@@ -3388,7 +3390,7 @@
         <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3483,7 +3485,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61685-2025</t>
+          <t>A 21700-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3497,10 +3499,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46002</v>
+        <v>45442</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,38 +3516,38 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3554,48 +3556,48 @@
         <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Klasefibbla
-Tvåblad
-Kärrknipprot</t>
+          <t>Töcknig trymal
+Skuggorangelav
+Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 61685-2025 artfynd.xlsx", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 61685-2025 karta.png", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 61685-2025 georefererad karta.tif", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 61685-2025 FSC-klagomål.docx", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 61685-2025 FSC-klagomål mail.docx", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 61685-2025 tillsynsbegäran.docx", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 61685-2025 tillsynsbegäran mail.docx", "A 61685-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21700-2024</t>
+          <t>A 4132-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3609,10 +3611,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45442</v>
+        <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3626,20 +3628,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>12.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -3654,60 +3656,59 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Töcknig trymal
-Skuggorangelav
-Scharlakansvårskål agg.</t>
+          <t>Bredgentiana
+Nästrot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 21700-2024 artfynd.xlsx", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 21700-2024 karta.png", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 21700-2024 georefererad karta.tif", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 21700-2024 FSC-klagomål.docx", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 21700-2024 FSC-klagomål mail.docx", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 21700-2024 tillsynsbegäran.docx", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 21700-2024 tillsynsbegäran mail.docx", "A 21700-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4132-2026</t>
+          <t>A 4133-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3724,7 +3725,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3742,7 +3743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.2</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
@@ -3754,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3766,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
@@ -3778,47 +3779,47 @@
         <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana
-Nästrot</t>
+          <t>Tvåblad
+Nattviol</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4132-2026 artfynd.xlsx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4132-2026 karta.png", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4132-2026 georefererad karta.tif", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4132-2026 FSC-klagomål.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4132-2026 FSC-klagomål mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4132-2026 tillsynsbegäran.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4132-2026 tillsynsbegäran mail.docx", "A 4132-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4133-2026</t>
+          <t>A 15739-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3832,10 +3833,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46044</v>
+        <v>45748</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3849,21 +3850,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3886,50 +3887,50 @@
         <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad
-Nattviol</t>
+          <t>Brunklöver
+Slåtterfibbla</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 4133-2026 artfynd.xlsx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 4133-2026 karta.png", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 4133-2026 georefererad karta.tif", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 4133-2026 FSC-klagomål.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 4133-2026 FSC-klagomål mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 4133-2026 tillsynsbegäran.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 4133-2026 tillsynsbegäran mail.docx", "A 4133-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15739-2025</t>
+          <t>A 58485-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3943,10 +3944,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45748</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,23 +3961,23 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3988,59 +3989,63 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver
-Slåtterfibbla</t>
+          <t>Knärot
+Myskmadra</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 15739-2025 artfynd.xlsx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 15739-2025 karta.png", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 15739-2025 georefererad karta.tif", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 15739-2025 FSC-klagomål.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 15739-2025 FSC-klagomål mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 15739-2025 tillsynsbegäran.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 15739-2025 tillsynsbegäran mail.docx", "A 15739-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58485-2025</t>
+          <t>A 40478-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4054,10 +4059,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45985</v>
+        <v>46295</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4071,11 +4076,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4087,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4099,10 +4104,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4111,68 +4116,68 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Myskmadra</t>
+          <t>Rödgul trumpetsvamp
+Järpe</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 58485-2025 artfynd.xlsx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40478-2026 artfynd.xlsx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 58485-2025 karta.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40478-2026 karta.png", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 58485-2025 georefererad karta.tif", "A 58485-2025")</f>
-        <v/>
-      </c>
-      <c r="Z31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/knärot/A 58485-2025 karta knärot.png", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40478-2026 georefererad karta.tif", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 58485-2025 FSC-klagomål.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40478-2026 FSC-klagomål.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 58485-2025 FSC-klagomål mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40478-2026 FSC-klagomål mail.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 58485-2025 tillsynsbegäran.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40478-2026 tillsynsbegäran.docx", "A 40478-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 58485-2025 tillsynsbegäran mail.docx", "A 58485-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40478-2026 tillsynsbegäran mail.docx", "A 40478-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 40478-2026 prioriterade fågelarter.docx", "A 40478-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40478-2026</t>
+          <t>S 780-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46295</v>
+        <v>45369</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,26 +4191,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4214,80 +4219,76 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
       </c>
       <c r="T32" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp
-Järpe</t>
+          <t>Mosippa
+Motaggsvamp</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 40478-2026 artfynd.xlsx", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 40478-2026 karta.png", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 40478-2026 georefererad karta.tif", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 40478-2026 FSC-klagomål.docx", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 40478-2026 FSC-klagomål mail.docx", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 40478-2026 tillsynsbegäran.docx", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 40478-2026 tillsynsbegäran mail.docx", "A 40478-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 40478-2026 prioriterade fågelarter.docx", "A 40478-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S 780-2024</t>
+          <t>A 10455-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45369</v>
+        <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4301,14 +4302,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4320,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4329,59 +4330,58 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mosippa
-Motaggsvamp</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/S 780-2024 artfynd.xlsx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/S 780-2024 karta.png", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/S 780-2024 georefererad karta.tif", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/S 780-2024 FSC-klagomål.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/S 780-2024 FSC-klagomål mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/S 780-2024 tillsynsbegäran.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/S 780-2024 tillsynsbegäran mail.docx", "S 780-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1673-2026</t>
+          <t>A 63004-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46034</v>
+        <v>46009</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -4449,49 +4449,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19303-2024</t>
+          <t>A 1673-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45428</v>
+        <v>46034</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4520,20 +4520,25 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4545,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4557,39 +4562,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 1673-2026 artfynd.xlsx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 1673-2026 karta.png", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 1673-2026 georefererad karta.tif", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 1673-2026 FSC-klagomål.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 1673-2026 FSC-klagomål mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 1673-2026 tillsynsbegäran.docx", "A 1673-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 1673-2026 tillsynsbegäran mail.docx", "A 1673-2026")</f>
         <v/>
       </c>
     </row>
@@ -4613,7 +4618,7 @@
         <v>46044</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4711,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19300-2024</t>
+          <t>A 51238-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4720,10 +4725,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45428</v>
+        <v>45947</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4735,8 +4740,13 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4745,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4760,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4772,50 +4782,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51238-2025</t>
+          <t>A 43285-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4829,10 +4835,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45947</v>
+        <v>45183</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4850,7 +4856,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4890,35 +4896,35 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 51238-2025 artfynd.xlsx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 51238-2025 karta.png", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 51238-2025 georefererad karta.tif", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 51238-2025 FSC-klagomål.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 51238-2025 FSC-klagomål mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 51238-2025 tillsynsbegäran.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 51238-2025 tillsynsbegäran mail.docx", "A 51238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
         <v/>
       </c>
     </row>
@@ -4942,7 +4948,7 @@
         <v>46099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5030,7 +5036,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57734-2025</t>
+          <t>A 70017-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5044,10 +5050,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45981</v>
+        <v>44533</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5059,13 +5065,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5077,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -5089,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5101,46 +5102,50 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7286-2023</t>
+          <t>A 57734-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5150,14 +5155,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44970</v>
+        <v>45981</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5175,19 +5180,19 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5199,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5215,42 +5220,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 57734-2025 artfynd.xlsx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 57734-2025 karta.png", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 57734-2025 georefererad karta.tif", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 57734-2025 FSC-klagomål.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 57734-2025 FSC-klagomål mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 57734-2025 tillsynsbegäran.docx", "A 57734-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 57734-2025 tillsynsbegäran mail.docx", "A 57734-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63004-2025</t>
+          <t>A 7286-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5260,14 +5265,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46009</v>
+        <v>44970</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,10 +5290,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -5318,49 +5323,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 63004-2025 artfynd.xlsx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 7286-2023 artfynd.xlsx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 63004-2025 karta.png", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 7286-2023 karta.png", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 63004-2025 georefererad karta.tif", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 7286-2023 georefererad karta.tif", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 63004-2025 FSC-klagomål.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 7286-2023 FSC-klagomål.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 63004-2025 FSC-klagomål mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 7286-2023 FSC-klagomål mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 63004-2025 tillsynsbegäran.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 7286-2023 tillsynsbegäran.docx", "A 7286-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 63004-2025 tillsynsbegäran mail.docx", "A 63004-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 7286-2023 tillsynsbegäran mail.docx", "A 7286-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62938-2025</t>
+          <t>A 30233-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46009</v>
+        <v>46206</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,11 +5396,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.2</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5431,46 +5436,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 62938-2025 artfynd.xlsx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30233-2026 artfynd.xlsx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 62938-2025 karta.png", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30233-2026 karta.png", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 62938-2025 georefererad karta.tif", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30233-2026 georefererad karta.tif", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 62938-2025 FSC-klagomål.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30233-2026 FSC-klagomål.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 62938-2025 FSC-klagomål mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30233-2026 FSC-klagomål mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 62938-2025 tillsynsbegäran.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30233-2026 tillsynsbegäran.docx", "A 30233-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 62938-2025 tillsynsbegäran mail.docx", "A 62938-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30233-2026 tillsynsbegäran mail.docx", "A 30233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10455-2022</t>
+          <t>A 30236-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5484,10 +5489,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44623</v>
+        <v>46206</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5505,16 +5510,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5529,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5538,49 +5543,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 10455-2022 artfynd.xlsx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 30236-2026 artfynd.xlsx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 10455-2022 karta.png", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 30236-2026 karta.png", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 10455-2022 georefererad karta.tif", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 30236-2026 georefererad karta.tif", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 10455-2022 FSC-klagomål.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 30236-2026 FSC-klagomål.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 10455-2022 FSC-klagomål mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 30236-2026 FSC-klagomål mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 10455-2022 tillsynsbegäran.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 30236-2026 tillsynsbegäran.docx", "A 30236-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 10455-2022 tillsynsbegäran mail.docx", "A 10455-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 30236-2026 tillsynsbegäran mail.docx", "A 30236-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 70017-2021</t>
+          <t>A 19303-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44533</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5610,7 +5615,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5622,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5634,10 +5639,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5650,46 +5655,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 70017-2021 artfynd.xlsx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19303-2024 artfynd.xlsx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 70017-2021 karta.png", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19303-2024 karta.png", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 70017-2021 georefererad karta.tif", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19303-2024 georefererad karta.tif", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 70017-2021 FSC-klagomål.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19303-2024 FSC-klagomål.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 70017-2021 FSC-klagomål mail.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19303-2024 FSC-klagomål mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 70017-2021 tillsynsbegäran.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19303-2024 tillsynsbegäran.docx", "A 19303-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 70017-2021 tillsynsbegäran mail.docx", "A 70017-2021")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 70017-2021 prioriterade fågelarter.docx", "A 70017-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19303-2024 tillsynsbegäran mail.docx", "A 19303-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19304-2024</t>
+          <t>A 3950-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5699,14 +5700,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5719,7 +5720,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5728,10 +5729,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5746,55 +5747,55 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19304-2024 artfynd.xlsx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 3950-2025 artfynd.xlsx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19304-2024 karta.png", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 3950-2025 karta.png", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19304-2024 georefererad karta.tif", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 3950-2025 georefererad karta.tif", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19304-2024 FSC-klagomål.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 3950-2025 FSC-klagomål.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19304-2024 FSC-klagomål mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 3950-2025 FSC-klagomål mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19304-2024 tillsynsbegäran.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 3950-2025 tillsynsbegäran.docx", "A 3950-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19304-2024 tillsynsbegäran mail.docx", "A 19304-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 3950-2025 tillsynsbegäran mail.docx", "A 3950-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43285-2023</t>
+          <t>A 19300-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5808,10 +5809,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45183</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5823,13 +5824,8 @@
           <t>ÄLVKARLEBY</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5838,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5853,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5865,46 +5861,50 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 43285-2023 artfynd.xlsx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/artfynd/A 19300-2024 artfynd.xlsx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 43285-2023 karta.png", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor/A 19300-2024 karta.png", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 43285-2023 georefererad karta.tif", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/kartor_geotiff/A 19300-2024 georefererad karta.tif", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 43285-2023 FSC-klagomål.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomål/A 19300-2024 FSC-klagomål.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 43285-2023 FSC-klagomål mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/klagomålsmail/A 19300-2024 FSC-klagomål mail.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 43285-2023 tillsynsbegäran.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsyn/A 19300-2024 tillsynsbegäran.docx", "A 19300-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 43285-2023 tillsynsbegäran mail.docx", "A 43285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/tillsynsmail/A 19300-2024 tillsynsbegäran mail.docx", "A 19300-2024")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0319/fåglar/A 19300-2024 prioriterade fågelarter.docx", "A 19300-2024")</f>
       